--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -1,28 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72036AA-AF99-4798-B200-813C945F4CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2287418-ACB8-428F-BA16-78685753FC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
-    <sheet name="Tools_Ko" sheetId="21" r:id="rId2"/>
-    <sheet name="Objects_En" sheetId="22" r:id="rId3"/>
+    <sheet name="Objects_En" sheetId="22" r:id="rId2"/>
+    <sheet name="Tools_Ko" sheetId="21" r:id="rId3"/>
     <sheet name="Tools_En" sheetId="23" r:id="rId4"/>
+    <sheet name="UI_Ko" sheetId="24" r:id="rId5"/>
+    <sheet name="UI_En" sheetId="25" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Objects_En!$B$6:$B$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Objects_En!$B$6:$B$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Objects_Ko!$B$6:$B$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Tools_En!$B$6:$B$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tools_Ko!$B$6:$B$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tools_Ko!$B$6:$B$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">UI_En!$B$5:$B$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">UI_Ko!$B$5:$B$144</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="357">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1213,6 +1217,62 @@
   </si>
   <si>
     <t>A place to store your items.</t>
+  </si>
+  <si>
+    <t>$$StringData_UI_Ko$$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$$StringData_UI_En$$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SeedShop_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VegeShop_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨앗 상점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소 가게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seed Shop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vege Shop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SeedShop_ClosedMessage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음에 방문해주세요..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VegeShop_ClosedMessage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여는 시간이 아닙니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Please come again next time.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We are not open yet.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1388,6 +1448,14 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1481,13 +1549,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="20481" name="Button 1" hidden="1">
+            <xdr:cNvPr id="21505" name="Button 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s20481"/>
+                  <a14:compatExt spid="_x0000_s21505"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001500000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001540000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1555,13 +1623,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="21505" name="Button 1" hidden="1">
+            <xdr:cNvPr id="20481" name="Button 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s21505"/>
+                  <a14:compatExt spid="_x0000_s20481"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001540000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001500000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1636,6 +1704,154 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000001580000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
+                </a:rPr>
+                <a:t>"." 값 제거 매크로</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>17</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="25601" name="Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s25601"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF4A3E9F-90CF-4277-92C6-4D0CF9656D52}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
+                </a:rPr>
+                <a:t>"." 값 제거 매크로</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>17</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="26625" name="Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s26625"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15029117-C377-4C62-B477-8D014D33ADE2}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3177,12 +3393,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB14FF3-77DA-4F15-BE17-E8C413F8CD5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D81EAC2-667C-41A3-A419-9DF06865FAE0}">
   <dimension ref="A3:AJ218"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="13.125" customWidth="1"/>
@@ -3205,7 +3421,7 @@
   <sheetData>
     <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>85</v>
+        <v>236</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -3274,10 +3490,10 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -3288,10 +3504,10 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" t="s">
-        <v>209</v>
+        <v>87</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>264</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -3302,10 +3518,10 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>211</v>
+        <v>265</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -3316,10 +3532,10 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>210</v>
+        <v>266</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -3330,10 +3546,10 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -3344,10 +3560,10 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>213</v>
+        <v>270</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -3358,10 +3574,10 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -3372,10 +3588,10 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>175</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -3386,10 +3602,10 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>176</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -3400,10 +3616,10 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -3414,10 +3630,10 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -3427,7 +3643,10 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>179</v>
+        <v>97</v>
+      </c>
+      <c r="B16" t="s">
+        <v>280</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
@@ -3436,10 +3655,10 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>180</v>
+        <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>219</v>
+        <v>285</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -3448,7 +3667,10 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>181</v>
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>286</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -3457,10 +3679,10 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>220</v>
+        <v>287</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -3469,7 +3691,10 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>101</v>
+      </c>
+      <c r="B20" t="s">
+        <v>288</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
@@ -3478,10 +3703,10 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>221</v>
+        <v>293</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
@@ -3490,10 +3715,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>222</v>
+        <v>294</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
@@ -3502,10 +3727,10 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>186</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>223</v>
+        <v>295</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
@@ -3514,7 +3739,10 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>187</v>
+        <v>105</v>
+      </c>
+      <c r="B24" t="s">
+        <v>296</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -3523,10 +3751,10 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="B25" t="s">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -3535,7 +3763,10 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>189</v>
+        <v>107</v>
+      </c>
+      <c r="B26" t="s">
+        <v>302</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -3544,10 +3775,10 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>190</v>
+        <v>108</v>
       </c>
       <c r="B27" t="s">
-        <v>225</v>
+        <v>303</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -3556,7 +3787,10 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>191</v>
+        <v>109</v>
+      </c>
+      <c r="B28" t="s">
+        <v>304</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -3565,10 +3799,10 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>226</v>
+        <v>309</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -3578,10 +3812,10 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>227</v>
+        <v>310</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -3591,10 +3825,10 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
-        <v>228</v>
+        <v>312</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -3604,7 +3838,10 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>195</v>
+        <v>113</v>
+      </c>
+      <c r="B32" t="s">
+        <v>311</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -3614,10 +3851,10 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>196</v>
+        <v>114</v>
       </c>
       <c r="B33" t="s">
-        <v>229</v>
+        <v>313</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
@@ -3626,7 +3863,10 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>197</v>
+        <v>115</v>
+      </c>
+      <c r="B34" t="s">
+        <v>314</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -3635,10 +3875,10 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s">
-        <v>230</v>
+        <v>315</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -3648,7 +3888,10 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>199</v>
+        <v>117</v>
+      </c>
+      <c r="B36" t="s">
+        <v>316</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -3658,10 +3901,10 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>231</v>
+        <v>317</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -3671,10 +3914,10 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="B38" t="s">
-        <v>232</v>
+        <v>318</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
@@ -3684,10 +3927,10 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="B39" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -3697,7 +3940,10 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>203</v>
+        <v>121</v>
+      </c>
+      <c r="B40" t="s">
+        <v>320</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
@@ -3707,10 +3953,10 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>204</v>
+        <v>122</v>
       </c>
       <c r="B41" t="s">
-        <v>234</v>
+        <v>321</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
@@ -3720,7 +3966,10 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>205</v>
+        <v>123</v>
+      </c>
+      <c r="B42" t="s">
+        <v>322</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
@@ -3730,10 +3979,10 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>206</v>
+        <v>124</v>
       </c>
       <c r="B43" t="s">
-        <v>235</v>
+        <v>325</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -3743,7 +3992,10 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>125</v>
+      </c>
+      <c r="B44" t="s">
+        <v>326</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -3752,11 +4004,339 @@
       <c r="P44" s="6"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" t="s">
+        <v>327</v>
+      </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>132</v>
+      </c>
+      <c r="B51" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>133</v>
+      </c>
+      <c r="B52" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>137</v>
+      </c>
+      <c r="B56" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>145</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>147</v>
+      </c>
+      <c r="B66" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>151</v>
+      </c>
+      <c r="B70" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>152</v>
+      </c>
+      <c r="B71" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>153</v>
+      </c>
+      <c r="B72" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>154</v>
+      </c>
+      <c r="B73" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>156</v>
+      </c>
+      <c r="B75" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>157</v>
+      </c>
+      <c r="B76" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>158</v>
+      </c>
+      <c r="B77" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>159</v>
+      </c>
+      <c r="B78" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>160</v>
+      </c>
+      <c r="B79" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>161</v>
+      </c>
+      <c r="B80" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>163</v>
+      </c>
+      <c r="B82" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>165</v>
+      </c>
+      <c r="B84" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>166</v>
+      </c>
+      <c r="B85" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>167</v>
+      </c>
+      <c r="B86" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="5"/>
@@ -3973,7 +4553,7 @@
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="20481" r:id="rId4" name="Button 1">
+            <control shapeId="21505" r:id="rId4" name="Button 1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!DeleteSpecificValueCells">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -4000,12 +4580,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D81EAC2-667C-41A3-A419-9DF06865FAE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB14FF3-77DA-4F15-BE17-E8C413F8CD5E}">
   <dimension ref="A3:AJ218"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="13.125" customWidth="1"/>
@@ -4028,7 +4608,7 @@
   <sheetData>
     <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>236</v>
+        <v>85</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4097,10 +4677,10 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -4111,10 +4691,10 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>264</v>
+        <v>169</v>
+      </c>
+      <c r="B6" t="s">
+        <v>209</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -4125,10 +4705,10 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -4139,10 +4719,10 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="B8" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -4153,10 +4733,10 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="B9" t="s">
-        <v>269</v>
+        <v>212</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -4167,10 +4747,10 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="B10" t="s">
-        <v>270</v>
+        <v>213</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -4181,10 +4761,10 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>174</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>214</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -4195,10 +4775,10 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>215</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -4209,10 +4789,10 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="B13" t="s">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -4223,10 +4803,10 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s">
-        <v>276</v>
+        <v>217</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -4237,10 +4817,10 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s">
-        <v>279</v>
+        <v>218</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -4250,10 +4830,7 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" t="s">
-        <v>280</v>
+        <v>179</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
@@ -4262,10 +4839,10 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s">
-        <v>285</v>
+        <v>219</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -4274,10 +4851,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" t="s">
-        <v>286</v>
+        <v>181</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -4286,10 +4860,10 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s">
-        <v>287</v>
+        <v>220</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -4298,10 +4872,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" t="s">
-        <v>288</v>
+        <v>183</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
@@ -4310,10 +4881,10 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s">
-        <v>293</v>
+        <v>221</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
@@ -4322,10 +4893,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s">
-        <v>294</v>
+        <v>222</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
@@ -4334,10 +4905,10 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="B23" t="s">
-        <v>295</v>
+        <v>223</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
@@ -4346,10 +4917,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" t="s">
-        <v>296</v>
+        <v>187</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -4358,10 +4926,10 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="B25" t="s">
-        <v>301</v>
+        <v>224</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -4370,10 +4938,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" t="s">
-        <v>302</v>
+        <v>189</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -4382,10 +4947,10 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>190</v>
       </c>
       <c r="B27" t="s">
-        <v>303</v>
+        <v>225</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -4394,10 +4959,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>109</v>
-      </c>
-      <c r="B28" t="s">
-        <v>304</v>
+        <v>191</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -4406,10 +4968,10 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="B29" t="s">
-        <v>309</v>
+        <v>226</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -4419,10 +4981,10 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="B30" t="s">
-        <v>310</v>
+        <v>227</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -4432,10 +4994,10 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="B31" t="s">
-        <v>312</v>
+        <v>228</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -4445,10 +5007,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>113</v>
-      </c>
-      <c r="B32" t="s">
-        <v>311</v>
+        <v>195</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -4458,10 +5017,10 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s">
-        <v>313</v>
+        <v>229</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
@@ -4470,10 +5029,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" t="s">
-        <v>314</v>
+        <v>197</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -4482,10 +5038,10 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s">
-        <v>315</v>
+        <v>230</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -4495,10 +5051,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" t="s">
-        <v>316</v>
+        <v>199</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -4508,10 +5061,10 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s">
-        <v>317</v>
+        <v>231</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -4521,10 +5074,10 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s">
-        <v>318</v>
+        <v>232</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
@@ -4534,10 +5087,10 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="B39" t="s">
-        <v>319</v>
+        <v>233</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -4547,10 +5100,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B40" t="s">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
@@ -4560,10 +5110,10 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>122</v>
+        <v>204</v>
       </c>
       <c r="B41" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
@@ -4573,10 +5123,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>123</v>
-      </c>
-      <c r="B42" t="s">
-        <v>322</v>
+        <v>205</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
@@ -4586,10 +5133,10 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>124</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s">
-        <v>325</v>
+        <v>235</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -4599,10 +5146,7 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>125</v>
-      </c>
-      <c r="B44" t="s">
-        <v>326</v>
+        <v>207</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -4611,339 +5155,11 @@
       <c r="P44" s="6"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" t="s">
-        <v>327</v>
-      </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>128</v>
-      </c>
-      <c r="B47" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>129</v>
-      </c>
-      <c r="B48" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>130</v>
-      </c>
-      <c r="B49" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>131</v>
-      </c>
-      <c r="B50" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>132</v>
-      </c>
-      <c r="B51" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>133</v>
-      </c>
-      <c r="B52" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>134</v>
-      </c>
-      <c r="B53" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>136</v>
-      </c>
-      <c r="B55" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>137</v>
-      </c>
-      <c r="B56" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>138</v>
-      </c>
-      <c r="B57" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>139</v>
-      </c>
-      <c r="B58" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>140</v>
-      </c>
-      <c r="B59" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>142</v>
-      </c>
-      <c r="B61" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>143</v>
-      </c>
-      <c r="B62" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>144</v>
-      </c>
-      <c r="B63" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>145</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>146</v>
-      </c>
-      <c r="B65" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>147</v>
-      </c>
-      <c r="B66" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>148</v>
-      </c>
-      <c r="B67" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>149</v>
-      </c>
-      <c r="B68" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>150</v>
-      </c>
-      <c r="B69" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>151</v>
-      </c>
-      <c r="B70" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>152</v>
-      </c>
-      <c r="B71" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>153</v>
-      </c>
-      <c r="B72" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>154</v>
-      </c>
-      <c r="B73" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>155</v>
-      </c>
-      <c r="B74" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>156</v>
-      </c>
-      <c r="B75" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>157</v>
-      </c>
-      <c r="B76" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>158</v>
-      </c>
-      <c r="B77" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>159</v>
-      </c>
-      <c r="B78" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>160</v>
-      </c>
-      <c r="B79" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>161</v>
-      </c>
-      <c r="B80" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>162</v>
-      </c>
-      <c r="B81" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>163</v>
-      </c>
-      <c r="B82" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>164</v>
-      </c>
-      <c r="B83" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>165</v>
-      </c>
-      <c r="B84" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>166</v>
-      </c>
-      <c r="B85" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>167</v>
-      </c>
-      <c r="B86" t="s">
-        <v>308</v>
-      </c>
     </row>
     <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="5"/>
@@ -5160,7 +5376,7 @@
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="21505" r:id="rId4" name="Button 1">
+            <control shapeId="20481" r:id="rId4" name="Button 1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!DeleteSpecificValueCells">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -5998,4 +6214,1150 @@
     </mc:Choice>
   </mc:AlternateContent>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1DEF80-1767-4678-9A0F-3D65DA9959F4}">
+  <dimension ref="A3:AJ212"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+    </row>
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="T5" s="6"/>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="T6" s="6"/>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="T7" s="6"/>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>353</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="T8" s="6"/>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="T9" s="6"/>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="P18" s="6"/>
+    </row>
+    <row r="19" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="P19" s="6"/>
+    </row>
+    <row r="20" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="P21" s="6"/>
+    </row>
+    <row r="22" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="9"/>
+      <c r="P23" s="6"/>
+    </row>
+    <row r="24" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="9"/>
+      <c r="P24" s="6"/>
+    </row>
+    <row r="25" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="9"/>
+      <c r="P25" s="6"/>
+    </row>
+    <row r="26" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="9"/>
+      <c r="P26" s="6"/>
+    </row>
+    <row r="27" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="P28" s="6"/>
+    </row>
+    <row r="29" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="9"/>
+      <c r="P29" s="6"/>
+    </row>
+    <row r="30" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="9"/>
+      <c r="P30" s="6"/>
+    </row>
+    <row r="31" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="9"/>
+      <c r="P31" s="6"/>
+    </row>
+    <row r="32" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="9"/>
+      <c r="P32" s="6"/>
+    </row>
+    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="9"/>
+      <c r="P33" s="6"/>
+    </row>
+    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="9"/>
+      <c r="P34" s="6"/>
+    </row>
+    <row r="35" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="9"/>
+      <c r="P35" s="6"/>
+    </row>
+    <row r="36" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="9"/>
+      <c r="P36" s="6"/>
+    </row>
+    <row r="37" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="9"/>
+      <c r="P37" s="6"/>
+    </row>
+    <row r="38" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="9"/>
+      <c r="P38" s="6"/>
+    </row>
+    <row r="39" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="9"/>
+      <c r="P39" s="6"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B145" s="5"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B146" s="5"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B147" s="5"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B148" s="5"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B149" s="5"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B150" s="5"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B151" s="5"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B152" s="5"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B153" s="5"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B154" s="5"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B155" s="5"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B156" s="5"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B157" s="5"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B158" s="5"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B159" s="5"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B160" s="5"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B161" s="5"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B162" s="5"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B163" s="5"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B164" s="5"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B165" s="5"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B166" s="5"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B167" s="5"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B168" s="5"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B169" s="5"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B170" s="5"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B171" s="5"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B172" s="5"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B173" s="5"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B174" s="5"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B175" s="5"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B176" s="5"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B177" s="5"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B178" s="5"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B179" s="5"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B180" s="5"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B181" s="5"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B182" s="5"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B183" s="5"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B184" s="5"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B185" s="5"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B186" s="5"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B187" s="5"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B188" s="5"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B189" s="5"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B190" s="5"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B191" s="5"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B192" s="5"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B193" s="5"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B194" s="5"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B195" s="5"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B196" s="5"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B197" s="5"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B198" s="5"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B199" s="5"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B200" s="5"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B201" s="5"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B202" s="5"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B203" s="5"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B204" s="5"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B205" s="5"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B206" s="5"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B207" s="5"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B208" s="5"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B209" s="5"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B210" s="5"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B211" s="5"/>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B212" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="25601" r:id="rId4" name="Button 1">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!DeleteSpecificValueCells">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>16</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>0</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>17</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448EFE5B-7539-4545-AC12-95181FCEF528}">
+  <dimension ref="A3:AJ206"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+    </row>
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B5" t="s">
+        <v>349</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="P5" s="6"/>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>353</v>
+      </c>
+      <c r="B8" t="s">
+        <v>356</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="P8" s="6"/>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="9"/>
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="9"/>
+      <c r="P18" s="6"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="9"/>
+      <c r="P19" s="6"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="9"/>
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="P21" s="6"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="9"/>
+      <c r="P23" s="6"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="9"/>
+      <c r="P24" s="6"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="9"/>
+      <c r="P25" s="6"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" s="9"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="9"/>
+      <c r="P26" s="6"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="9"/>
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="9"/>
+      <c r="P28" s="6"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="9"/>
+      <c r="P29" s="6"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="9"/>
+      <c r="P30" s="6"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="9"/>
+      <c r="P31" s="6"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="9"/>
+      <c r="P32" s="6"/>
+    </row>
+    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="9"/>
+      <c r="P33" s="6"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B139" s="5"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B140" s="5"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B141" s="5"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B142" s="5"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B143" s="5"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B144" s="5"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B145" s="5"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B146" s="5"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B147" s="5"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B148" s="5"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B149" s="5"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B150" s="5"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B151" s="5"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B152" s="5"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B153" s="5"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B154" s="5"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B155" s="5"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B156" s="5"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B157" s="5"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B158" s="5"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B159" s="5"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B160" s="5"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B161" s="5"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B162" s="5"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B163" s="5"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B164" s="5"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B165" s="5"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B166" s="5"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B167" s="5"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B168" s="5"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B169" s="5"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B170" s="5"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B171" s="5"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B172" s="5"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B173" s="5"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B174" s="5"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B175" s="5"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B176" s="5"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B177" s="5"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B178" s="5"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B179" s="5"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B180" s="5"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B181" s="5"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B182" s="5"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B183" s="5"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B184" s="5"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B185" s="5"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B186" s="5"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B187" s="5"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B188" s="5"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B189" s="5"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B190" s="5"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B191" s="5"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B192" s="5"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B193" s="5"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B194" s="5"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B195" s="5"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B196" s="5"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B197" s="5"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B198" s="5"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B199" s="5"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B200" s="5"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B201" s="5"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B202" s="5"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B203" s="5"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B204" s="5"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B205" s="5"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B206" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="26625" r:id="rId4" name="Button 1">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!DeleteSpecificValueCells">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>16</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>0</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>17</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
 </file>
--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2287418-ACB8-428F-BA16-78685753FC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8B0E23-42FD-4059-9D61-4F90DC657FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="372">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1272,6 +1272,66 @@
   </si>
   <si>
     <t>We are not open yet.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Animal Product</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vegetable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crafiting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동물 생산품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야채</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꽃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제작</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1555,7 +1615,7 @@
                   <a14:compatExt spid="_x0000_s21505"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001540000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001540000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1629,7 +1689,7 @@
                   <a14:compatExt spid="_x0000_s20481"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001500000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001500000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1777,7 +1837,7 @@
                   <a14:compatExt spid="_x0000_s25601"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF4A3E9F-90CF-4277-92C6-4D0CF9656D52}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000001640000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1851,7 +1911,7 @@
                   <a14:compatExt spid="_x0000_s26625"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15029117-C377-4C62-B477-8D014D33ADE2}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000001680000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6369,6 +6429,12 @@
       <c r="T8" s="6"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>357</v>
+      </c>
+      <c r="B9" t="s">
+        <v>358</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -6376,145 +6442,193 @@
       <c r="T9" s="6"/>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>359</v>
+      </c>
+      <c r="B10" t="s">
+        <v>366</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>360</v>
+      </c>
+      <c r="B11" t="s">
+        <v>367</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B12" t="s">
+        <v>368</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>362</v>
+      </c>
+      <c r="B13" t="s">
+        <v>369</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>363</v>
+      </c>
+      <c r="B14" t="s">
+        <v>370</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>338</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>364</v>
+      </c>
+      <c r="B16" t="s">
+        <v>371</v>
+      </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>365</v>
+      </c>
+      <c r="B17" t="s">
+        <v>347</v>
+      </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
@@ -6956,6 +7070,12 @@
       <c r="P8" s="6"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>357</v>
+      </c>
+      <c r="B9" t="s">
+        <v>357</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8B0E23-42FD-4059-9D61-4F90DC657FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A929AA99-4363-4233-B006-CA227C8B45BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="373">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1332,6 +1332,10 @@
   </si>
   <si>
     <t>제작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨앗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6530,7 +6534,7 @@
         <v>365</v>
       </c>
       <c r="B17" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -7082,109 +7086,157 @@
       <c r="P9" s="6"/>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>359</v>
+      </c>
+      <c r="B10" t="s">
+        <v>359</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>360</v>
+      </c>
+      <c r="B11" t="s">
+        <v>360</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B12" t="s">
+        <v>361</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>362</v>
+      </c>
+      <c r="B13" t="s">
+        <v>362</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>363</v>
+      </c>
+      <c r="B14" t="s">
+        <v>363</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>338</v>
+      </c>
+      <c r="B15" t="s">
+        <v>338</v>
+      </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>364</v>
+      </c>
+      <c r="B16" t="s">
+        <v>364</v>
+      </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>365</v>
+      </c>
+      <c r="B17" t="s">
+        <v>365</v>
+      </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B26" s="9"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -7192,42 +7244,42 @@
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A929AA99-4363-4233-B006-CA227C8B45BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5086E529-CD6E-45CE-8AE6-34C9A8BA03B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="7" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -19,14 +19,18 @@
     <sheet name="Tools_En" sheetId="23" r:id="rId4"/>
     <sheet name="UI_Ko" sheetId="24" r:id="rId5"/>
     <sheet name="UI_En" sheetId="25" r:id="rId6"/>
+    <sheet name="Location_Ko" sheetId="26" r:id="rId7"/>
+    <sheet name="Location_En" sheetId="27" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Location_En!$B$5:$B$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Location_Ko!$B$5:$B$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Objects_En!$B$6:$B$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Objects_Ko!$B$6:$B$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Tools_En!$B$6:$B$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tools_Ko!$B$6:$B$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">UI_En!$B$5:$B$138</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">UI_Ko!$B$5:$B$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">UI_En!$B$5:$B$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">UI_Ko!$B$5:$B$142</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="375">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1251,30 +1255,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SeedShop_ClosedMessage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다음에 방문해주세요..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VegeShop_ClosedMessage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여는 시간이 아닙니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Please come again next time.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>We are not open yet.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Buy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1336,6 +1316,38 @@
   </si>
   <si>
     <t>씨앗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$$StringData_Location_Ko$$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$$StringData_Location_En$$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Closed_OpenRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SeedShop_Closed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 일요일 휴무.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>It's closed… (Open {0} - {1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영업 종료…(여는 시간 {0} - {1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Closed on Sundays.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1517,6 +1529,14 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
@@ -1964,6 +1984,154 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>17</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="31745" name="Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s31745"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1FADDE-3FFB-4E24-94D9-9A9FECE817BA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
+                </a:rPr>
+                <a:t>"." 값 제거 매크로</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>17</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="32769" name="Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s32769"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFE5D9F7-1298-478D-A83D-2A56F4C751DD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
+                </a:rPr>
+                <a:t>"." 값 제거 매크로</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
@@ -6282,11 +6450,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1DEF80-1767-4678-9A0F-3D65DA9959F4}">
-  <dimension ref="A3:AJ212"/>
+  <dimension ref="A3:AJ210"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="13.125" customWidth="1"/>
@@ -6411,7 +6579,6 @@
       <c r="B7" t="s">
         <v>352</v>
       </c>
-      <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6423,34 +6590,31 @@
         <v>353</v>
       </c>
       <c r="B8" t="s">
-        <v>354</v>
-      </c>
-      <c r="D8" s="6"/>
+        <v>360</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="P8" s="6"/>
-      <c r="T8" s="6"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B9" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
-      <c r="T9" s="6"/>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B10" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -6459,10 +6623,10 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B11" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -6471,10 +6635,10 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B12" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -6483,10 +6647,10 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="B13" t="s">
-        <v>369</v>
+        <v>69</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -6495,10 +6659,10 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B14" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -6507,10 +6671,10 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>366</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -6518,121 +6682,111 @@
       <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>364</v>
-      </c>
-      <c r="B16" t="s">
-        <v>371</v>
-      </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>365</v>
-      </c>
-      <c r="B17" t="s">
-        <v>372</v>
-      </c>
+    <row r="17" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
+      <c r="H21" s="9"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
+      <c r="H22" s="9"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
+      <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
+      <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
@@ -6674,19 +6828,11 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-      <c r="P38" s="6"/>
-    </row>
-    <row r="39" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-      <c r="P39" s="6"/>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B143" s="5"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B144" s="5"/>
     </row>
     <row r="145" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B145" s="5"/>
@@ -6885,12 +7031,6 @@
     </row>
     <row r="210" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B210" s="5"/>
-    </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B211" s="5"/>
-    </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B212" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6931,11 +7071,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448EFE5B-7539-4545-AC12-95181FCEF528}">
-  <dimension ref="A3:AJ206"/>
+  <dimension ref="A3:AJ204"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="13.125" customWidth="1"/>
@@ -7054,7 +7194,7 @@
         <v>351</v>
       </c>
       <c r="B7" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -7066,7 +7206,7 @@
         <v>353</v>
       </c>
       <c r="B8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -7075,10 +7215,10 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -7087,10 +7227,10 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B10" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -7099,10 +7239,10 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -7111,10 +7251,10 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B12" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -7123,10 +7263,10 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="B13" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -7135,10 +7275,10 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B14" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -7147,151 +7287,133 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="B15" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
+      <c r="H15" s="9"/>
       <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>364</v>
-      </c>
-      <c r="B16" t="s">
-        <v>364</v>
-      </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
+      <c r="H16" s="9"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>365</v>
-      </c>
-      <c r="B17" t="s">
-        <v>365</v>
-      </c>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
+      <c r="H21" s="9"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
+      <c r="H22" s="9"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B24" s="9"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B26" s="9"/>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-      <c r="P32" s="6"/>
-    </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-      <c r="P33" s="6"/>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B137" s="5"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B138" s="5"/>
     </row>
     <row r="139" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B139" s="5"/>
@@ -7490,12 +7612,6 @@
     </row>
     <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="5"/>
-    </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B205" s="5"/>
-    </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B206" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7532,4 +7648,1126 @@
     </mc:Choice>
   </mc:AlternateContent>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D9F6-C7CE-4D6D-A307-34F0A02C664A}">
+  <dimension ref="A3:AJ212"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+    </row>
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B5" t="s">
+        <v>373</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="T5" s="6"/>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="T6" s="6"/>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="T7" s="6"/>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="T8" s="6"/>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="T9" s="6"/>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="P18" s="6"/>
+    </row>
+    <row r="19" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="P19" s="6"/>
+    </row>
+    <row r="20" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="P21" s="6"/>
+    </row>
+    <row r="22" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="9"/>
+      <c r="P23" s="6"/>
+    </row>
+    <row r="24" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="9"/>
+      <c r="P24" s="6"/>
+    </row>
+    <row r="25" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="9"/>
+      <c r="P25" s="6"/>
+    </row>
+    <row r="26" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="9"/>
+      <c r="P26" s="6"/>
+    </row>
+    <row r="27" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="P28" s="6"/>
+    </row>
+    <row r="29" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="9"/>
+      <c r="P29" s="6"/>
+    </row>
+    <row r="30" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="9"/>
+      <c r="P30" s="6"/>
+    </row>
+    <row r="31" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="9"/>
+      <c r="P31" s="6"/>
+    </row>
+    <row r="32" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="9"/>
+      <c r="P32" s="6"/>
+    </row>
+    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="9"/>
+      <c r="P33" s="6"/>
+    </row>
+    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="9"/>
+      <c r="P34" s="6"/>
+    </row>
+    <row r="35" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="9"/>
+      <c r="P35" s="6"/>
+    </row>
+    <row r="36" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="9"/>
+      <c r="P36" s="6"/>
+    </row>
+    <row r="37" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="9"/>
+      <c r="P37" s="6"/>
+    </row>
+    <row r="38" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="9"/>
+      <c r="P38" s="6"/>
+    </row>
+    <row r="39" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="9"/>
+      <c r="P39" s="6"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B145" s="5"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B146" s="5"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B147" s="5"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B148" s="5"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B149" s="5"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B150" s="5"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B151" s="5"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B152" s="5"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B153" s="5"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B154" s="5"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B155" s="5"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B156" s="5"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B157" s="5"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B158" s="5"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B159" s="5"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B160" s="5"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B161" s="5"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B162" s="5"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B163" s="5"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B164" s="5"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B165" s="5"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B166" s="5"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B167" s="5"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B168" s="5"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B169" s="5"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B170" s="5"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B171" s="5"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B172" s="5"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B173" s="5"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B174" s="5"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B175" s="5"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B176" s="5"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B177" s="5"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B178" s="5"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B179" s="5"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B180" s="5"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B181" s="5"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B182" s="5"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B183" s="5"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B184" s="5"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B185" s="5"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B186" s="5"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B187" s="5"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B188" s="5"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B189" s="5"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B190" s="5"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B191" s="5"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B192" s="5"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B193" s="5"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B194" s="5"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B195" s="5"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B196" s="5"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B197" s="5"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B198" s="5"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B199" s="5"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B200" s="5"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B201" s="5"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B202" s="5"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B203" s="5"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B204" s="5"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B205" s="5"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B206" s="5"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B207" s="5"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B208" s="5"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B209" s="5"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B210" s="5"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B211" s="5"/>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B212" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="31745" r:id="rId4" name="Button 1">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!DeleteSpecificValueCells">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>16</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>0</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>17</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC371501-4D80-4BA3-AE38-ACD1D9A5C0BD}">
+  <dimension ref="A3:AJ206"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+    </row>
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B5" t="s">
+        <v>372</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="P5" s="6"/>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="P8" s="6"/>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="9"/>
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="9"/>
+      <c r="P18" s="6"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="9"/>
+      <c r="P19" s="6"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="9"/>
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="P21" s="6"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="9"/>
+      <c r="P23" s="6"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="9"/>
+      <c r="P24" s="6"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="9"/>
+      <c r="P25" s="6"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" s="9"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="9"/>
+      <c r="P26" s="6"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="9"/>
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="9"/>
+      <c r="P28" s="6"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="9"/>
+      <c r="P29" s="6"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="9"/>
+      <c r="P30" s="6"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="9"/>
+      <c r="P31" s="6"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="9"/>
+      <c r="P32" s="6"/>
+    </row>
+    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="9"/>
+      <c r="P33" s="6"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B139" s="5"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B140" s="5"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B141" s="5"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B142" s="5"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B143" s="5"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B144" s="5"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B145" s="5"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B146" s="5"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B147" s="5"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B148" s="5"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B149" s="5"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B150" s="5"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B151" s="5"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B152" s="5"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B153" s="5"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B154" s="5"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B155" s="5"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B156" s="5"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B157" s="5"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B158" s="5"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B159" s="5"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B160" s="5"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B161" s="5"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B162" s="5"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B163" s="5"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B164" s="5"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B165" s="5"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B166" s="5"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B167" s="5"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B168" s="5"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B169" s="5"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B170" s="5"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B171" s="5"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B172" s="5"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B173" s="5"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B174" s="5"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B175" s="5"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B176" s="5"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B177" s="5"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B178" s="5"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B179" s="5"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B180" s="5"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B181" s="5"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B182" s="5"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B183" s="5"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B184" s="5"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B185" s="5"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B186" s="5"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B187" s="5"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B188" s="5"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B189" s="5"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B190" s="5"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B191" s="5"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B192" s="5"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B193" s="5"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B194" s="5"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B195" s="5"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B196" s="5"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B197" s="5"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B198" s="5"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B199" s="5"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B200" s="5"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B201" s="5"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B202" s="5"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B203" s="5"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B204" s="5"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B205" s="5"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B206" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="32769" r:id="rId4" name="Button 1">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!DeleteSpecificValueCells">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>16</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>0</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>17</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
 </file>
--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5086E529-CD6E-45CE-8AE6-34C9A8BA03B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C1AFB3-9EC3-4089-987C-757B145B0264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="7" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -29,8 +29,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Objects_Ko!$B$6:$B$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Tools_En!$B$6:$B$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tools_Ko!$B$6:$B$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">UI_En!$B$5:$B$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">UI_Ko!$B$5:$B$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">UI_En!$B$5:$B$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">UI_Ko!$B$5:$B$143</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="377">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1348,6 +1348,14 @@
   </si>
   <si>
     <t>Closed on Sundays.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>판매</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2009,7 +2017,7 @@
                   <a14:compatExt spid="_x0000_s31745"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1FADDE-3FFB-4E24-94D9-9A9FECE817BA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-0000017C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2083,7 +2091,7 @@
                   <a14:compatExt spid="_x0000_s32769"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFE5D9F7-1298-478D-A83D-2A56F4C751DD}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000001800000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6450,7 +6458,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1DEF80-1767-4678-9A0F-3D65DA9959F4}">
-  <dimension ref="A3:AJ210"/>
+  <dimension ref="A3:AJ211"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
@@ -6587,22 +6595,23 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="B8" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="P8" s="6"/>
+      <c r="T8" s="6"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -6611,10 +6620,10 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -6623,10 +6632,10 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -6635,10 +6644,10 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -6647,10 +6656,10 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>364</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -6659,10 +6668,10 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="B14" t="s">
-        <v>365</v>
+        <v>69</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -6671,10 +6680,10 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B15" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -6682,6 +6691,12 @@
       <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>359</v>
+      </c>
+      <c r="B16" t="s">
+        <v>366</v>
+      </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -6715,7 +6730,6 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
       <c r="P21" s="6"/>
     </row>
     <row r="22" spans="5:16" x14ac:dyDescent="0.3">
@@ -6743,6 +6757,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
+      <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
     <row r="26" spans="5:16" x14ac:dyDescent="0.3">
@@ -6755,7 +6770,6 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
     <row r="28" spans="5:16" x14ac:dyDescent="0.3">
@@ -6828,8 +6842,12 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B143" s="5"/>
+    <row r="38" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="9"/>
+      <c r="P38" s="6"/>
     </row>
     <row r="144" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B144" s="5"/>
@@ -7031,6 +7049,9 @@
     </row>
     <row r="210" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B210" s="5"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B211" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7071,7 +7092,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448EFE5B-7539-4545-AC12-95181FCEF528}">
-  <dimension ref="A3:AJ204"/>
+  <dimension ref="A3:AJ205"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
@@ -7203,10 +7224,10 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="B8" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -7215,10 +7236,10 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -7227,10 +7248,10 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -7239,10 +7260,10 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -7251,10 +7272,10 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -7263,10 +7284,10 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="B13" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -7275,10 +7296,10 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="B14" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -7287,18 +7308,23 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B15" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
       <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>359</v>
+      </c>
+      <c r="B16" t="s">
+        <v>359</v>
+      </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -7323,6 +7349,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
+      <c r="H19" s="9"/>
       <c r="P19" s="6"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
@@ -7335,7 +7362,6 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
       <c r="P21" s="6"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
@@ -7353,7 +7379,6 @@
       <c r="P23" s="6"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B24" s="9"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -7361,6 +7386,7 @@
       <c r="P24" s="6"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B25" s="9"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -7409,8 +7435,12 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B137" s="5"/>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="9"/>
+      <c r="P32" s="6"/>
     </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B138" s="5"/>
@@ -7612,6 +7642,9 @@
     </row>
     <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="5"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B205" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C1AFB3-9EC3-4089-987C-757B145B0264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AC56D0-E14C-4333-86BC-D36054AC797A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="840" yWindow="0" windowWidth="28770" windowHeight="15450" firstSheet="3" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="412">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1356,6 +1356,146 @@
   </si>
   <si>
     <t>판매</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NewGame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새 게임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Load</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불러오기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나가기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FarmName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>농장 이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HairColor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머리 색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Back</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Farm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>농장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fri</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>토</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Game</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Farm Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hair Color</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6702,105 +6842,201 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>377</v>
+      </c>
+      <c r="B17" t="s">
+        <v>378</v>
+      </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B18" t="s">
+        <v>380</v>
+      </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B19" t="s">
+        <v>382</v>
+      </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>383</v>
+      </c>
+      <c r="B20" t="s">
+        <v>384</v>
+      </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>385</v>
+      </c>
+      <c r="B21" t="s">
+        <v>386</v>
+      </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>387</v>
+      </c>
+      <c r="B22" t="s">
+        <v>388</v>
+      </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="9"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>389</v>
+      </c>
+      <c r="B23" t="s">
+        <v>390</v>
+      </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>391</v>
+      </c>
+      <c r="B24" t="s">
+        <v>392</v>
+      </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>393</v>
+      </c>
+      <c r="B25" t="s">
+        <v>394</v>
+      </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>395</v>
+      </c>
+      <c r="B26" t="s">
+        <v>402</v>
+      </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>396</v>
+      </c>
+      <c r="B27" t="s">
+        <v>403</v>
+      </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>397</v>
+      </c>
+      <c r="B28" t="s">
+        <v>404</v>
+      </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>398</v>
+      </c>
+      <c r="B29" t="s">
+        <v>405</v>
+      </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>399</v>
+      </c>
+      <c r="B30" t="s">
+        <v>406</v>
+      </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>400</v>
+      </c>
+      <c r="B31" t="s">
+        <v>407</v>
+      </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>401</v>
+      </c>
+      <c r="B32" t="s">
+        <v>408</v>
+      </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
@@ -7331,111 +7567,206 @@
       <c r="H16" s="9"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>377</v>
+      </c>
+      <c r="B17" t="s">
+        <v>409</v>
+      </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B18" t="s">
+        <v>379</v>
+      </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B19" t="s">
+        <v>381</v>
+      </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>383</v>
+      </c>
+      <c r="B20" t="s">
+        <v>383</v>
+      </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>385</v>
+      </c>
+      <c r="B21" t="s">
+        <v>410</v>
+      </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>387</v>
+      </c>
+      <c r="B22" t="s">
+        <v>387</v>
+      </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="9"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>389</v>
+      </c>
+      <c r="B23" t="s">
+        <v>411</v>
+      </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>391</v>
+      </c>
+      <c r="B24" t="s">
+        <v>391</v>
+      </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B25" s="9"/>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>393</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>393</v>
+      </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>395</v>
+      </c>
+      <c r="B26" t="s">
+        <v>395</v>
+      </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>396</v>
+      </c>
+      <c r="B27" t="s">
+        <v>396</v>
+      </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>397</v>
+      </c>
+      <c r="B28" t="s">
+        <v>397</v>
+      </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>398</v>
+      </c>
+      <c r="B29" t="s">
+        <v>398</v>
+      </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>399</v>
+      </c>
+      <c r="B30" t="s">
+        <v>399</v>
+      </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>400</v>
+      </c>
+      <c r="B31" t="s">
+        <v>400</v>
+      </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>401</v>
+      </c>
+      <c r="B32" t="s">
+        <v>401</v>
+      </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AC56D0-E14C-4333-86BC-D36054AC797A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66246FDB-5CA8-422B-9308-424BEF77B8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="840" yWindow="0" windowWidth="28770" windowHeight="15450" firstSheet="3" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="418">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1496,6 +1496,29 @@
   </si>
   <si>
     <t>Hair Color</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초기화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InputName</t>
+  </si>
+  <si>
+    <t>InputName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름을 입력하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7043,42 +7066,54 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>412</v>
+      </c>
+      <c r="B33" t="s">
+        <v>413</v>
+      </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>415</v>
+      </c>
+      <c r="B34" t="s">
+        <v>416</v>
+      </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
@@ -7773,6 +7808,22 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>412</v>
+      </c>
+      <c r="B33" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>414</v>
+      </c>
+      <c r="B34" t="s">
+        <v>417</v>
+      </c>
+    </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B138" s="5"/>
     </row>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66246FDB-5CA8-422B-9308-424BEF77B8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10162E70-8151-4254-A5A0-E2E114B58D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="430">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1519,6 +1519,54 @@
   </si>
   <si>
     <t>Input Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPRING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUMMER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FALL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WINTER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>봄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가을</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>겨울</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Summer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7093,6 +7141,12 @@
       <c r="P34" s="6"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>419</v>
+      </c>
+      <c r="B35" t="s">
+        <v>423</v>
+      </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
@@ -7100,6 +7154,12 @@
       <c r="P35" s="6"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>420</v>
+      </c>
+      <c r="B36" t="s">
+        <v>424</v>
+      </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
@@ -7107,6 +7167,12 @@
       <c r="P36" s="6"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>421</v>
+      </c>
+      <c r="B37" t="s">
+        <v>425</v>
+      </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
@@ -7114,6 +7180,12 @@
       <c r="P37" s="6"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>422</v>
+      </c>
+      <c r="B38" t="s">
+        <v>426</v>
+      </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
@@ -7824,6 +7896,38 @@
         <v>417</v>
       </c>
     </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>419</v>
+      </c>
+      <c r="B35" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>420</v>
+      </c>
+      <c r="B36" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>421</v>
+      </c>
+      <c r="B37" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>422</v>
+      </c>
+      <c r="B38" t="s">
+        <v>429</v>
+      </c>
+    </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B138" s="5"/>
     </row>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10162E70-8151-4254-A5A0-E2E114B58D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07D380D-383B-4BBD-8388-41ADD794E36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="436">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1567,6 +1567,30 @@
   </si>
   <si>
     <t>Winter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Am</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>am</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오후</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7192,6 +7216,22 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>430</v>
+      </c>
+      <c r="B39" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>432</v>
+      </c>
+      <c r="B40" t="s">
+        <v>435</v>
+      </c>
+    </row>
     <row r="144" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B144" s="5"/>
     </row>
@@ -7928,6 +7968,22 @@
         <v>429</v>
       </c>
     </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>430</v>
+      </c>
+      <c r="B39" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>432</v>
+      </c>
+      <c r="B40" t="s">
+        <v>433</v>
+      </c>
+    </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B138" s="5"/>
     </row>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eunyounggil/Documents/GitHub/Farm/Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07D380D-383B-4BBD-8388-41ADD794E36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE0EE6E-3220-364C-9ACA-B62646B116F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -29,10 +29,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Objects_Ko!$B$6:$B$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Tools_En!$B$6:$B$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tools_Ko!$B$6:$B$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">UI_En!$B$5:$B$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">UI_Ko!$B$5:$B$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">UI_En!$B$5:$B$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">UI_Ko!$B$5:$B$144</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +44,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -53,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="439">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1593,12 +1592,24 @@
     <t>오후</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Tool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fruit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1638,13 +1649,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1662,6 +1666,13 @@
       <color rgb="FF202122"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1721,7 +1732,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1730,7 +1741,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1830,7 +1841,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -1841,8 +1852,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕"/>
-                  <a:ea typeface="맑은 고딕"/>
+                  <a:latin typeface="맑은 고딕" charset="-127"/>
+                  <a:ea typeface="맑은 고딕" charset="-127"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -1904,7 +1915,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -1915,8 +1926,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕"/>
-                  <a:ea typeface="맑은 고딕"/>
+                  <a:latin typeface="맑은 고딕" charset="-127"/>
+                  <a:ea typeface="맑은 고딕" charset="-127"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -1978,7 +1989,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -1989,8 +2000,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕"/>
-                  <a:ea typeface="맑은 고딕"/>
+                  <a:latin typeface="맑은 고딕" charset="-127"/>
+                  <a:ea typeface="맑은 고딕" charset="-127"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2052,7 +2063,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2063,8 +2074,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕"/>
-                  <a:ea typeface="맑은 고딕"/>
+                  <a:latin typeface="맑은 고딕" charset="-127"/>
+                  <a:ea typeface="맑은 고딕" charset="-127"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2126,7 +2137,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2137,8 +2148,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕"/>
-                  <a:ea typeface="맑은 고딕"/>
+                  <a:latin typeface="맑은 고딕" charset="-127"/>
+                  <a:ea typeface="맑은 고딕" charset="-127"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2200,7 +2211,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2211,8 +2222,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕"/>
-                  <a:ea typeface="맑은 고딕"/>
+                  <a:latin typeface="맑은 고딕" charset="-127"/>
+                  <a:ea typeface="맑은 고딕" charset="-127"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2274,7 +2285,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2285,8 +2296,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕"/>
-                  <a:ea typeface="맑은 고딕"/>
+                  <a:latin typeface="맑은 고딕" charset="-127"/>
+                  <a:ea typeface="맑은 고딕" charset="-127"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2348,7 +2359,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2359,8 +2370,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕"/>
-                  <a:ea typeface="맑은 고딕"/>
+                  <a:latin typeface="맑은 고딕" charset="-127"/>
+                  <a:ea typeface="맑은 고딕" charset="-127"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2376,9 +2387,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2416,7 +2427,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2522,7 +2533,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2664,7 +2675,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2674,31 +2685,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB82EE84-0108-42B1-826D-C63A5B94B9EE}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A3:AJ218"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.375" customWidth="1"/>
+    <col min="23" max="32" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2737,7 +2748,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -2767,7 +2778,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -2781,7 +2792,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -2795,7 +2806,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -2809,7 +2820,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -2823,7 +2834,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -2837,7 +2848,7 @@
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -2851,7 +2862,7 @@
       <c r="P10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>92</v>
       </c>
@@ -2865,7 +2876,7 @@
       <c r="P11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -2879,7 +2890,7 @@
       <c r="P12" s="6"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -2893,7 +2904,7 @@
       <c r="P13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>95</v>
       </c>
@@ -2907,7 +2918,7 @@
       <c r="P14" s="6"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -2920,7 +2931,7 @@
       <c r="P15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -2932,7 +2943,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -2944,7 +2955,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>99</v>
       </c>
@@ -2956,7 +2967,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -2968,7 +2979,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>101</v>
       </c>
@@ -2980,7 +2991,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -2992,7 +3003,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -3004,7 +3015,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -3016,7 +3027,7 @@
       <c r="G23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -3028,7 +3039,7 @@
       <c r="G24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -3040,7 +3051,7 @@
       <c r="G25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -3052,7 +3063,7 @@
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -3064,7 +3075,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>109</v>
       </c>
@@ -3076,7 +3087,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -3089,7 +3100,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -3102,7 +3113,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -3115,7 +3126,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -3128,7 +3139,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>114</v>
       </c>
@@ -3140,7 +3151,7 @@
       <c r="G33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>115</v>
       </c>
@@ -3152,7 +3163,7 @@
       <c r="G34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>116</v>
       </c>
@@ -3165,7 +3176,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>117</v>
       </c>
@@ -3178,7 +3189,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -3191,7 +3202,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>119</v>
       </c>
@@ -3204,7 +3215,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>120</v>
       </c>
@@ -3217,7 +3228,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>121</v>
       </c>
@@ -3230,7 +3241,7 @@
       <c r="H40" s="9"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>122</v>
       </c>
@@ -3243,7 +3254,7 @@
       <c r="H41" s="9"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -3256,7 +3267,7 @@
       <c r="H42" s="9"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>124</v>
       </c>
@@ -3269,7 +3280,7 @@
       <c r="H43" s="9"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>125</v>
       </c>
@@ -3282,7 +3293,7 @@
       <c r="H44" s="9"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>126</v>
       </c>
@@ -3295,7 +3306,7 @@
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>127</v>
       </c>
@@ -3303,7 +3314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>128</v>
       </c>
@@ -3311,7 +3322,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>129</v>
       </c>
@@ -3319,7 +3330,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>130</v>
       </c>
@@ -3327,7 +3338,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>131</v>
       </c>
@@ -3335,7 +3346,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>132</v>
       </c>
@@ -3343,7 +3354,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>133</v>
       </c>
@@ -3351,7 +3362,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>134</v>
       </c>
@@ -3359,7 +3370,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>135</v>
       </c>
@@ -3367,7 +3378,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>136</v>
       </c>
@@ -3375,7 +3386,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>137</v>
       </c>
@@ -3383,7 +3394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>138</v>
       </c>
@@ -3391,7 +3402,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>139</v>
       </c>
@@ -3399,7 +3410,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>140</v>
       </c>
@@ -3407,7 +3418,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>141</v>
       </c>
@@ -3415,7 +3426,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>142</v>
       </c>
@@ -3423,7 +3434,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>143</v>
       </c>
@@ -3431,7 +3442,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>144</v>
       </c>
@@ -3439,7 +3450,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>145</v>
       </c>
@@ -3447,7 +3458,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>146</v>
       </c>
@@ -3455,7 +3466,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>147</v>
       </c>
@@ -3463,7 +3474,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>148</v>
       </c>
@@ -3471,7 +3482,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>149</v>
       </c>
@@ -3479,7 +3490,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>150</v>
       </c>
@@ -3487,7 +3498,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>151</v>
       </c>
@@ -3495,7 +3506,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -3503,7 +3514,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>153</v>
       </c>
@@ -3511,7 +3522,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>154</v>
       </c>
@@ -3519,7 +3530,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>155</v>
       </c>
@@ -3527,7 +3538,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>156</v>
       </c>
@@ -3535,7 +3546,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>157</v>
       </c>
@@ -3543,7 +3554,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>158</v>
       </c>
@@ -3551,7 +3562,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>159</v>
       </c>
@@ -3559,7 +3570,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>160</v>
       </c>
@@ -3567,7 +3578,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2">
       <c r="A80" t="s">
         <v>161</v>
       </c>
@@ -3575,7 +3586,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>162</v>
       </c>
@@ -3583,7 +3594,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -3591,7 +3602,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>164</v>
       </c>
@@ -3599,7 +3610,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>165</v>
       </c>
@@ -3607,7 +3618,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>166</v>
       </c>
@@ -3615,7 +3626,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
         <v>167</v>
       </c>
@@ -3623,208 +3634,208 @@
         <v>42</v>
       </c>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:2">
       <c r="B212" s="5"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:2">
       <c r="B213" s="5"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:2">
       <c r="B214" s="5"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:2">
       <c r="B215" s="5"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:2">
       <c r="B216" s="5"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:2">
       <c r="B217" s="5"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:2">
       <c r="B218" s="5"/>
     </row>
   </sheetData>
@@ -3870,31 +3881,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D81EAC2-667C-41A3-A419-9DF06865FAE0}">
   <dimension ref="A3:AJ218"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.375" customWidth="1"/>
+    <col min="23" max="32" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>236</v>
       </c>
@@ -3933,7 +3944,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -3963,7 +3974,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -3977,7 +3988,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -3991,7 +4002,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -4005,7 +4016,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -4019,7 +4030,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -4033,7 +4044,7 @@
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -4047,7 +4058,7 @@
       <c r="P10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>92</v>
       </c>
@@ -4061,7 +4072,7 @@
       <c r="P11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -4075,7 +4086,7 @@
       <c r="P12" s="6"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -4089,7 +4100,7 @@
       <c r="P13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>95</v>
       </c>
@@ -4103,7 +4114,7 @@
       <c r="P14" s="6"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -4116,7 +4127,7 @@
       <c r="P15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -4128,7 +4139,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -4140,7 +4151,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>99</v>
       </c>
@@ -4152,7 +4163,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -4164,7 +4175,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>101</v>
       </c>
@@ -4176,7 +4187,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -4188,7 +4199,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -4200,7 +4211,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -4212,7 +4223,7 @@
       <c r="G23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -4224,7 +4235,7 @@
       <c r="G24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -4236,7 +4247,7 @@
       <c r="G25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -4248,7 +4259,7 @@
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -4260,7 +4271,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>109</v>
       </c>
@@ -4272,7 +4283,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -4285,7 +4296,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -4298,7 +4309,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -4311,7 +4322,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -4324,7 +4335,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>114</v>
       </c>
@@ -4336,7 +4347,7 @@
       <c r="G33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>115</v>
       </c>
@@ -4348,7 +4359,7 @@
       <c r="G34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>116</v>
       </c>
@@ -4361,7 +4372,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>117</v>
       </c>
@@ -4374,7 +4385,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -4387,7 +4398,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>119</v>
       </c>
@@ -4400,7 +4411,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>120</v>
       </c>
@@ -4413,7 +4424,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>121</v>
       </c>
@@ -4426,7 +4437,7 @@
       <c r="H40" s="9"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>122</v>
       </c>
@@ -4439,7 +4450,7 @@
       <c r="H41" s="9"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -4452,7 +4463,7 @@
       <c r="H42" s="9"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>124</v>
       </c>
@@ -4465,7 +4476,7 @@
       <c r="H43" s="9"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>125</v>
       </c>
@@ -4478,7 +4489,7 @@
       <c r="H44" s="9"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>126</v>
       </c>
@@ -4491,7 +4502,7 @@
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>127</v>
       </c>
@@ -4499,7 +4510,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>128</v>
       </c>
@@ -4507,7 +4518,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>129</v>
       </c>
@@ -4515,7 +4526,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>130</v>
       </c>
@@ -4523,7 +4534,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>131</v>
       </c>
@@ -4531,7 +4542,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>132</v>
       </c>
@@ -4539,7 +4550,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>133</v>
       </c>
@@ -4547,7 +4558,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>134</v>
       </c>
@@ -4555,12 +4566,12 @@
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>136</v>
       </c>
@@ -4568,7 +4579,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>137</v>
       </c>
@@ -4576,7 +4587,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>138</v>
       </c>
@@ -4584,7 +4595,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>139</v>
       </c>
@@ -4592,7 +4603,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>140</v>
       </c>
@@ -4600,12 +4611,12 @@
         <v>338</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>142</v>
       </c>
@@ -4613,7 +4624,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>143</v>
       </c>
@@ -4621,7 +4632,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>144</v>
       </c>
@@ -4629,7 +4640,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>145</v>
       </c>
@@ -4637,7 +4648,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>146</v>
       </c>
@@ -4645,7 +4656,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>147</v>
       </c>
@@ -4653,7 +4664,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>148</v>
       </c>
@@ -4661,7 +4672,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>149</v>
       </c>
@@ -4669,7 +4680,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>150</v>
       </c>
@@ -4677,7 +4688,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>151</v>
       </c>
@@ -4685,7 +4696,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -4693,7 +4704,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>153</v>
       </c>
@@ -4701,7 +4712,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>154</v>
       </c>
@@ -4709,7 +4720,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>155</v>
       </c>
@@ -4717,7 +4728,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>156</v>
       </c>
@@ -4725,7 +4736,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>157</v>
       </c>
@@ -4733,7 +4744,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>158</v>
       </c>
@@ -4741,7 +4752,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>159</v>
       </c>
@@ -4749,7 +4760,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>160</v>
       </c>
@@ -4757,7 +4768,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2">
       <c r="A80" t="s">
         <v>161</v>
       </c>
@@ -4765,7 +4776,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>162</v>
       </c>
@@ -4773,7 +4784,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -4781,7 +4792,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>164</v>
       </c>
@@ -4789,7 +4800,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>165</v>
       </c>
@@ -4797,7 +4808,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>166</v>
       </c>
@@ -4805,7 +4816,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
         <v>167</v>
       </c>
@@ -4813,208 +4824,208 @@
         <v>308</v>
       </c>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:2">
       <c r="B212" s="5"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:2">
       <c r="B213" s="5"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:2">
       <c r="B214" s="5"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:2">
       <c r="B215" s="5"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:2">
       <c r="B216" s="5"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:2">
       <c r="B217" s="5"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:2">
       <c r="B218" s="5"/>
     </row>
   </sheetData>
@@ -5057,31 +5068,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB14FF3-77DA-4F15-BE17-E8C413F8CD5E}">
   <dimension ref="A3:AJ218"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.375" customWidth="1"/>
+    <col min="23" max="32" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>85</v>
       </c>
@@ -5120,7 +5131,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -5150,7 +5161,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -5164,7 +5175,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>169</v>
       </c>
@@ -5178,7 +5189,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>170</v>
       </c>
@@ -5192,7 +5203,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>171</v>
       </c>
@@ -5206,7 +5217,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -5220,7 +5231,7 @@
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>173</v>
       </c>
@@ -5234,7 +5245,7 @@
       <c r="P10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>174</v>
       </c>
@@ -5248,7 +5259,7 @@
       <c r="P11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>175</v>
       </c>
@@ -5262,7 +5273,7 @@
       <c r="P12" s="6"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>176</v>
       </c>
@@ -5276,7 +5287,7 @@
       <c r="P13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>177</v>
       </c>
@@ -5290,7 +5301,7 @@
       <c r="P14" s="6"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>178</v>
       </c>
@@ -5303,7 +5314,7 @@
       <c r="P15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -5312,7 +5323,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>180</v>
       </c>
@@ -5324,7 +5335,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>181</v>
       </c>
@@ -5333,7 +5344,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -5345,7 +5356,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>183</v>
       </c>
@@ -5354,7 +5365,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>184</v>
       </c>
@@ -5366,7 +5377,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>185</v>
       </c>
@@ -5378,7 +5389,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>186</v>
       </c>
@@ -5390,7 +5401,7 @@
       <c r="G23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>187</v>
       </c>
@@ -5399,7 +5410,7 @@
       <c r="G24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>188</v>
       </c>
@@ -5411,7 +5422,7 @@
       <c r="G25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>189</v>
       </c>
@@ -5420,7 +5431,7 @@
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -5432,7 +5443,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>191</v>
       </c>
@@ -5441,7 +5452,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>192</v>
       </c>
@@ -5454,7 +5465,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>193</v>
       </c>
@@ -5467,7 +5478,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>194</v>
       </c>
@@ -5480,7 +5491,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>195</v>
       </c>
@@ -5490,7 +5501,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>196</v>
       </c>
@@ -5502,7 +5513,7 @@
       <c r="G33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -5511,7 +5522,7 @@
       <c r="G34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>198</v>
       </c>
@@ -5524,7 +5535,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>199</v>
       </c>
@@ -5534,7 +5545,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>200</v>
       </c>
@@ -5547,7 +5558,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>201</v>
       </c>
@@ -5560,7 +5571,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>202</v>
       </c>
@@ -5573,7 +5584,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -5583,7 +5594,7 @@
       <c r="H40" s="9"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>204</v>
       </c>
@@ -5596,7 +5607,7 @@
       <c r="H41" s="9"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -5606,7 +5617,7 @@
       <c r="H42" s="9"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>206</v>
       </c>
@@ -5619,7 +5630,7 @@
       <c r="H43" s="9"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>207</v>
       </c>
@@ -5629,215 +5640,215 @@
       <c r="H44" s="9"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:2">
       <c r="B212" s="5"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:2">
       <c r="B213" s="5"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:2">
       <c r="B214" s="5"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:2">
       <c r="B215" s="5"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:2">
       <c r="B216" s="5"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:2">
       <c r="B217" s="5"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:2">
       <c r="B218" s="5"/>
     </row>
   </sheetData>
@@ -5880,31 +5891,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC7F4074-9E65-434B-897B-FD6EE64CA765}">
   <dimension ref="A3:AJ218"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.375" customWidth="1"/>
+    <col min="23" max="32" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>237</v>
       </c>
@@ -5943,7 +5954,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -5973,7 +5984,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -5987,7 +5998,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>169</v>
       </c>
@@ -6001,7 +6012,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>170</v>
       </c>
@@ -6015,7 +6026,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>171</v>
       </c>
@@ -6026,7 +6037,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -6040,7 +6051,7 @@
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>173</v>
       </c>
@@ -6051,7 +6062,7 @@
       <c r="P10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>174</v>
       </c>
@@ -6065,7 +6076,7 @@
       <c r="P11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>175</v>
       </c>
@@ -6076,7 +6087,7 @@
       <c r="P12" s="6"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>176</v>
       </c>
@@ -6090,7 +6101,7 @@
       <c r="P13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>177</v>
       </c>
@@ -6104,7 +6115,7 @@
       <c r="P14" s="6"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>178</v>
       </c>
@@ -6117,7 +6128,7 @@
       <c r="P15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -6126,7 +6137,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>180</v>
       </c>
@@ -6138,7 +6149,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>181</v>
       </c>
@@ -6147,7 +6158,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -6159,7 +6170,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>183</v>
       </c>
@@ -6168,7 +6179,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>184</v>
       </c>
@@ -6180,7 +6191,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>185</v>
       </c>
@@ -6192,7 +6203,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>186</v>
       </c>
@@ -6204,7 +6215,7 @@
       <c r="G23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>187</v>
       </c>
@@ -6213,7 +6224,7 @@
       <c r="G24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>188</v>
       </c>
@@ -6225,7 +6236,7 @@
       <c r="G25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>189</v>
       </c>
@@ -6234,7 +6245,7 @@
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -6246,7 +6257,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>191</v>
       </c>
@@ -6255,7 +6266,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>192</v>
       </c>
@@ -6268,7 +6279,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>193</v>
       </c>
@@ -6281,7 +6292,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>194</v>
       </c>
@@ -6294,7 +6305,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>195</v>
       </c>
@@ -6304,7 +6315,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>196</v>
       </c>
@@ -6316,7 +6327,7 @@
       <c r="G33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -6325,7 +6336,7 @@
       <c r="G34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>198</v>
       </c>
@@ -6338,7 +6349,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>199</v>
       </c>
@@ -6348,7 +6359,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>200</v>
       </c>
@@ -6361,7 +6372,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>201</v>
       </c>
@@ -6374,7 +6385,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>202</v>
       </c>
@@ -6387,7 +6398,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -6397,7 +6408,7 @@
       <c r="H40" s="9"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>204</v>
       </c>
@@ -6410,7 +6421,7 @@
       <c r="H41" s="9"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -6420,7 +6431,7 @@
       <c r="H42" s="9"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>206</v>
       </c>
@@ -6433,7 +6444,7 @@
       <c r="H43" s="9"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>207</v>
       </c>
@@ -6443,215 +6454,215 @@
       <c r="H44" s="9"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:2">
       <c r="B212" s="5"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:2">
       <c r="B213" s="5"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:2">
       <c r="B214" s="5"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:2">
       <c r="B215" s="5"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:2">
       <c r="B216" s="5"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:2">
       <c r="B217" s="5"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:2">
       <c r="B218" s="5"/>
     </row>
   </sheetData>
@@ -6693,32 +6704,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1DEF80-1767-4678-9A0F-3D65DA9959F4}">
-  <dimension ref="A3:AJ211"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A3:AJ212"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.375" customWidth="1"/>
+    <col min="23" max="32" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>343</v>
       </c>
@@ -6757,7 +6768,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -6787,7 +6798,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>345</v>
       </c>
@@ -6801,7 +6812,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>346</v>
       </c>
@@ -6815,7 +6826,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>351</v>
       </c>
@@ -6828,7 +6839,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>375</v>
       </c>
@@ -6841,7 +6852,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>353</v>
       </c>
@@ -6853,7 +6864,7 @@
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>354</v>
       </c>
@@ -6865,7 +6876,7 @@
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>355</v>
       </c>
@@ -6877,7 +6888,7 @@
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>356</v>
       </c>
@@ -6889,7 +6900,7 @@
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>357</v>
       </c>
@@ -6901,7 +6912,7 @@
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>338</v>
       </c>
@@ -6913,7 +6924,7 @@
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>358</v>
       </c>
@@ -6925,97 +6936,96 @@
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
-        <v>359</v>
+        <v>436</v>
       </c>
       <c r="B16" t="s">
-        <v>366</v>
+        <v>438</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="B17" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B18" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B19" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B20" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B22" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B23" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
@@ -7023,12 +7033,12 @@
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B24" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -7036,12 +7046,12 @@
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B25" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -7049,49 +7059,49 @@
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B26" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
+      <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B27" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B28" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B29" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -7099,12 +7109,12 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B30" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -7112,12 +7122,12 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B31" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -7125,12 +7135,12 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B32" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -7138,12 +7148,12 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B33" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
@@ -7151,12 +7161,12 @@
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B34" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -7164,12 +7174,12 @@
       <c r="H34" s="9"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B35" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -7177,12 +7187,12 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B36" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -7190,12 +7200,12 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B37" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -7203,12 +7213,12 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B38" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
@@ -7216,225 +7226,238 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
+        <v>422</v>
+      </c>
+      <c r="B39" t="s">
+        <v>426</v>
+      </c>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="9"/>
+      <c r="P39" s="6"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" t="s">
         <v>430</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="41" spans="1:16">
+      <c r="A41" t="s">
         <v>432</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B144" s="5"/>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:2">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:2">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:2">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:2">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:2">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:2">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2">
       <c r="B211" s="5"/>
+    </row>
+    <row r="212" spans="2:2">
+      <c r="B212" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7475,32 +7498,32 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448EFE5B-7539-4545-AC12-95181FCEF528}">
-  <dimension ref="A3:AJ205"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A3:AJ206"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.375" customWidth="1"/>
+    <col min="23" max="32" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>344</v>
       </c>
@@ -7539,7 +7562,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -7569,7 +7592,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>345</v>
       </c>
@@ -7581,7 +7604,7 @@
       <c r="G5" s="6"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>346</v>
       </c>
@@ -7593,7 +7616,7 @@
       <c r="G6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>351</v>
       </c>
@@ -7605,7 +7628,7 @@
       <c r="G7" s="6"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>375</v>
       </c>
@@ -7617,7 +7640,7 @@
       <c r="G8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>353</v>
       </c>
@@ -7629,7 +7652,7 @@
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>354</v>
       </c>
@@ -7641,7 +7664,7 @@
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>355</v>
       </c>
@@ -7653,7 +7676,7 @@
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>356</v>
       </c>
@@ -7665,7 +7688,7 @@
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>357</v>
       </c>
@@ -7677,7 +7700,7 @@
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>338</v>
       </c>
@@ -7689,7 +7712,7 @@
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>358</v>
       </c>
@@ -7701,25 +7724,24 @@
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
-        <v>359</v>
+        <v>436</v>
       </c>
       <c r="B16" t="s">
-        <v>359</v>
+        <v>436</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="B17" t="s">
-        <v>409</v>
+        <v>359</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -7727,12 +7749,12 @@
       <c r="H17" s="9"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B18" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -7740,12 +7762,12 @@
       <c r="H18" s="9"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -7753,49 +7775,49 @@
       <c r="H19" s="9"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
+      <c r="H20" s="9"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B21" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B22" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B23" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
@@ -7803,12 +7825,12 @@
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B24" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -7816,12 +7838,12 @@
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>393</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>393</v>
+        <v>391</v>
+      </c>
+      <c r="B25" t="s">
+        <v>391</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -7829,12 +7851,12 @@
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>395</v>
-      </c>
-      <c r="B26" t="s">
-        <v>395</v>
+        <v>393</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>393</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -7842,12 +7864,12 @@
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B27" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -7855,12 +7877,12 @@
       <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B28" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -7868,12 +7890,12 @@
       <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -7881,12 +7903,12 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B30" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -7894,12 +7916,12 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B31" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -7907,12 +7929,12 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B32" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -7920,273 +7942,366 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
+        <v>401</v>
+      </c>
+      <c r="B33" t="s">
+        <v>401</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="9"/>
+      <c r="P33" s="6"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" t="s">
         <v>412</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="35" spans="1:16">
+      <c r="A35" t="s">
         <v>414</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="36" spans="1:16">
+      <c r="A36" t="s">
         <v>419</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:16">
+      <c r="A37" t="s">
         <v>420</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="38" spans="1:16">
+      <c r="A38" t="s">
         <v>421</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="39" spans="1:16">
+      <c r="A39" t="s">
         <v>422</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="40" spans="1:16">
+      <c r="A40" t="s">
         <v>430</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="41" spans="1:16">
+      <c r="A41" t="s">
         <v>432</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B138" s="5"/>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
+      <c r="A42" t="s">
+        <v>353</v>
+      </c>
+      <c r="B42" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" t="s">
+        <v>354</v>
+      </c>
+      <c r="B43" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" t="s">
+        <v>355</v>
+      </c>
+      <c r="B44" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" t="s">
+        <v>356</v>
+      </c>
+      <c r="B45" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" t="s">
+        <v>357</v>
+      </c>
+      <c r="B46" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" t="s">
+        <v>338</v>
+      </c>
+      <c r="B47" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" t="s">
+        <v>358</v>
+      </c>
+      <c r="B48" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>359</v>
+      </c>
+      <c r="B49" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>436</v>
+      </c>
+      <c r="B50" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>437</v>
+      </c>
+      <c r="B51" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2">
       <c r="B139" s="5"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:2">
       <c r="B140" s="5"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:2">
       <c r="B141" s="5"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:2">
       <c r="B142" s="5"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:2">
       <c r="B143" s="5"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:2">
       <c r="B144" s="5"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:2">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:2">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:2">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:2">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:2">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:2">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
+    </row>
+    <row r="206" spans="2:2">
+      <c r="B206" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8228,31 +8343,31 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D9F6-C7CE-4D6D-A307-34F0A02C664A}">
   <dimension ref="A3:AJ212"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.375" customWidth="1"/>
+    <col min="23" max="32" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>367</v>
       </c>
@@ -8291,7 +8406,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -8321,7 +8436,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>369</v>
       </c>
@@ -8335,7 +8450,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>370</v>
       </c>
@@ -8349,7 +8464,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -8357,7 +8472,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -8365,410 +8480,410 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:16">
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:16">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:16">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:16">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:16">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:16">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:16">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:16">
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:16">
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:16">
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:16">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:16">
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:16">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:16">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:16">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:16">
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:16">
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:16">
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:16">
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:16">
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="5:16">
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="5:16">
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:16">
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:2">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:2">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:2">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:2">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:2">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:2">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:2">
       <c r="B212" s="5"/>
     </row>
   </sheetData>
@@ -8811,31 +8926,31 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC371501-4D80-4BA3-AE38-ACD1D9A5C0BD}">
   <dimension ref="A3:AJ206"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="18.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.375" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.375" customWidth="1"/>
+    <col min="23" max="32" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>368</v>
       </c>
@@ -8874,7 +8989,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -8904,7 +9019,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>369</v>
       </c>
@@ -8916,7 +9031,7 @@
       <c r="G5" s="6"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>370</v>
       </c>
@@ -8928,128 +9043,128 @@
       <c r="G6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16">
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16">
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16">
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16">
       <c r="B26" s="9"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -9057,257 +9172,257 @@
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16">
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16">
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:16">
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:2">
       <c r="B139" s="5"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:2">
       <c r="B140" s="5"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:2">
       <c r="B141" s="5"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:2">
       <c r="B142" s="5"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:2">
       <c r="B143" s="5"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:2">
       <c r="B144" s="5"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:2">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:2">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:2">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:2">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:2">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:2">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
   </sheetData>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eunyounggil/Documents/GitHub/Farm/Sheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE0EE6E-3220-364C-9ACA-B62646B116F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE86E66-0E20-4056-976C-C5E37AA46FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="15150" windowHeight="15585" firstSheet="2" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -26,13 +26,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Location_En!$B$5:$B$138</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Location_Ko!$B$5:$B$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Objects_En!$B$6:$B$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Objects_Ko!$B$6:$B$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Objects_Ko!$B$6:$B$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Tools_En!$B$6:$B$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tools_Ko!$B$6:$B$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">UI_En!$B$5:$B$138</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">UI_Ko!$B$5:$B$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">UI_En!$B$5:$B$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">UI_Ko!$B$5:$B$134</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,6 +44,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="516">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1604,12 +1605,311 @@
     <t>도구</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Salt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Butter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Creamy Veggie Soup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potato Gratin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carrot Muffin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parsnip Soup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Salt_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oli_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Butter_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Creamy Veggie Soup_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bread_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potato Gratin_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carrot Muffin_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parsnip Soup_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kale Seeds_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Salt_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oli_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Butter_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Creamy Veggie Soup_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bread_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potato Gratin_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carrot Muffin_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parsnip Soup_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소금</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>짠맛을 더해 요리의 완성도를 높여주는 조미료.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요리에 사용하는 기본 식용유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크림을 굳힌 동물성 지방 음식에 고소한 맛과 고소한 향을 더해 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부드러운 야채 수프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>각종 야채가 들어간 크림 수프.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 식사용 빵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감자 그라탕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감자를 얇게 썰어 크림과 버터로 노릇하게 구워낸 요리.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근 머핀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근을 곱게 다져 밀가루와 함께 오븐에 구운 달콤한 머핀.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파스닙 수프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파스닙과 우유로 끓인 뜨거운 크림 수프.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carrot Muffin Recipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bread Recipe_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potato Gratin Recipe_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carrot Muffin Recipe_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parsnip Soup Recipe_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bread Recipe_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potato Gratin Recipe_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carrot Muffin Recipe_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parsnip Soup Recipe_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Creamy Veggie Soup Recipe_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Creamy Veggie Soup Recipe_Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부드러운 야채 수프 레시피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빵 레시피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감자 그라탕 레시피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근 머핀 레시피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파스닙 수프 레시피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Creamy Veggie Soup Recipe</t>
+  </si>
+  <si>
+    <t>Bread Recipe</t>
+  </si>
+  <si>
+    <t>Potato Gratin Recipe</t>
+  </si>
+  <si>
+    <t>Parsnip Soup Recipe</t>
+  </si>
+  <si>
+    <t>Oil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A seasoning that adds saltiness and improves the overall quality of cooked dishes.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A basic cooking oil used in everyday cooking.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A dairy fat made by solidifying cream. Adds a rich, savory flavor and aroma to food.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A smooth cream soup made with a variety of vegetables</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic bread used as a staple food.</t>
+  </si>
+  <si>
+    <t>Thinly sliced potatoes baked golden brown with cream and butter.</t>
+  </si>
+  <si>
+    <t>A sweet muffin made by finely grating carrots and baking them with flour in an oven.</t>
+  </si>
+  <si>
+    <t>A warm cream soup made by boiling parsnips in milk.</t>
+  </si>
+  <si>
+    <t>Artisan Goods</t>
+  </si>
+  <si>
+    <t>장인 제작품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제작법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1661,18 +1961,41 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF202122"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1704,7 +2027,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1741,7 +2064,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1841,7 +2200,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -1852,8 +2211,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕" charset="-127"/>
-                  <a:ea typeface="맑은 고딕" charset="-127"/>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -1915,7 +2274,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -1926,8 +2285,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕" charset="-127"/>
-                  <a:ea typeface="맑은 고딕" charset="-127"/>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -1989,7 +2348,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2000,8 +2359,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕" charset="-127"/>
-                  <a:ea typeface="맑은 고딕" charset="-127"/>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2063,7 +2422,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2074,8 +2433,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕" charset="-127"/>
-                  <a:ea typeface="맑은 고딕" charset="-127"/>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2137,7 +2496,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2148,8 +2507,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕" charset="-127"/>
-                  <a:ea typeface="맑은 고딕" charset="-127"/>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2211,7 +2570,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2222,8 +2581,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕" charset="-127"/>
-                  <a:ea typeface="맑은 고딕" charset="-127"/>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2285,7 +2644,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2296,8 +2655,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕" charset="-127"/>
-                  <a:ea typeface="맑은 고딕" charset="-127"/>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2359,7 +2718,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2370,8 +2729,8 @@
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="맑은 고딕" charset="-127"/>
-                  <a:ea typeface="맑은 고딕" charset="-127"/>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
                 </a:rPr>
                 <a:t>"." 값 제거 매크로</a:t>
               </a:r>
@@ -2387,9 +2746,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2427,7 +2786,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2533,7 +2892,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2675,7 +3034,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2684,32 +3043,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB82EE84-0108-42B1-826D-C63A5B94B9EE}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A3:AJ218"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <dimension ref="A3:AJ229"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="131.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.33203125" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2748,7 +3107,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -2778,7 +3137,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -2792,7 +3151,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -2806,7 +3165,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -2820,7 +3179,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -2834,7 +3193,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -2848,7 +3207,7 @@
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -2862,7 +3221,7 @@
       <c r="P10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>92</v>
       </c>
@@ -2876,7 +3235,7 @@
       <c r="P11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -2890,7 +3249,7 @@
       <c r="P12" s="6"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -2904,7 +3263,7 @@
       <c r="P13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>95</v>
       </c>
@@ -2918,7 +3277,7 @@
       <c r="P14" s="6"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -2931,7 +3290,7 @@
       <c r="P15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -2943,7 +3302,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -2955,7 +3314,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>99</v>
       </c>
@@ -2967,7 +3326,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -2979,7 +3338,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>101</v>
       </c>
@@ -2991,7 +3350,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -3003,7 +3362,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -3015,7 +3374,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -3027,7 +3386,7 @@
       <c r="G23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -3039,7 +3398,7 @@
       <c r="G24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -3051,7 +3410,7 @@
       <c r="G25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -3063,7 +3422,7 @@
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -3075,7 +3434,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>109</v>
       </c>
@@ -3087,7 +3446,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -3100,7 +3459,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -3113,7 +3472,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -3126,7 +3485,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -3139,7 +3498,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>114</v>
       </c>
@@ -3151,7 +3510,7 @@
       <c r="G33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>115</v>
       </c>
@@ -3163,7 +3522,7 @@
       <c r="G34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>116</v>
       </c>
@@ -3176,7 +3535,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>117</v>
       </c>
@@ -3189,7 +3548,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -3202,7 +3561,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>119</v>
       </c>
@@ -3215,7 +3574,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>120</v>
       </c>
@@ -3228,7 +3587,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>121</v>
       </c>
@@ -3241,7 +3600,7 @@
       <c r="H40" s="9"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>122</v>
       </c>
@@ -3254,7 +3613,7 @@
       <c r="H41" s="9"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -3267,7 +3626,7 @@
       <c r="H42" s="9"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>124</v>
       </c>
@@ -3280,7 +3639,7 @@
       <c r="H43" s="9"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>125</v>
       </c>
@@ -3293,7 +3652,7 @@
       <c r="H44" s="9"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>126</v>
       </c>
@@ -3306,7 +3665,7 @@
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>127</v>
       </c>
@@ -3314,7 +3673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>128</v>
       </c>
@@ -3322,7 +3681,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>129</v>
       </c>
@@ -3330,7 +3689,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>130</v>
       </c>
@@ -3338,7 +3697,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>131</v>
       </c>
@@ -3346,7 +3705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>132</v>
       </c>
@@ -3354,7 +3713,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>133</v>
       </c>
@@ -3362,7 +3721,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>134</v>
       </c>
@@ -3370,7 +3729,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>135</v>
       </c>
@@ -3378,7 +3737,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>136</v>
       </c>
@@ -3386,7 +3745,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>137</v>
       </c>
@@ -3394,7 +3753,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>138</v>
       </c>
@@ -3402,7 +3761,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>139</v>
       </c>
@@ -3410,7 +3769,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>140</v>
       </c>
@@ -3418,7 +3777,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>141</v>
       </c>
@@ -3426,7 +3785,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>142</v>
       </c>
@@ -3434,7 +3793,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>143</v>
       </c>
@@ -3442,7 +3801,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>144</v>
       </c>
@@ -3450,7 +3809,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>145</v>
       </c>
@@ -3458,7 +3817,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>146</v>
       </c>
@@ -3466,7 +3825,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>147</v>
       </c>
@@ -3474,7 +3833,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>148</v>
       </c>
@@ -3482,7 +3841,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>149</v>
       </c>
@@ -3490,7 +3849,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>150</v>
       </c>
@@ -3498,7 +3857,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>151</v>
       </c>
@@ -3506,7 +3865,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -3514,7 +3873,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>153</v>
       </c>
@@ -3522,7 +3881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>154</v>
       </c>
@@ -3530,7 +3889,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>155</v>
       </c>
@@ -3538,7 +3897,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>156</v>
       </c>
@@ -3546,7 +3905,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>157</v>
       </c>
@@ -3554,7 +3913,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>158</v>
       </c>
@@ -3562,7 +3921,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>159</v>
       </c>
@@ -3570,7 +3929,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>160</v>
       </c>
@@ -3578,7 +3937,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>161</v>
       </c>
@@ -3586,7 +3945,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>162</v>
       </c>
@@ -3594,7 +3953,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -3602,7 +3961,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>164</v>
       </c>
@@ -3610,7 +3969,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>165</v>
       </c>
@@ -3618,7 +3977,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>166</v>
       </c>
@@ -3626,217 +3985,410 @@
         <v>82</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>167</v>
+        <v>454</v>
       </c>
       <c r="B86" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="151" spans="2:2">
-      <c r="B151" s="5"/>
-    </row>
-    <row r="152" spans="2:2">
-      <c r="B152" s="5"/>
-    </row>
-    <row r="153" spans="2:2">
-      <c r="B153" s="5"/>
-    </row>
-    <row r="154" spans="2:2">
-      <c r="B154" s="5"/>
-    </row>
-    <row r="155" spans="2:2">
-      <c r="B155" s="5"/>
-    </row>
-    <row r="156" spans="2:2">
-      <c r="B156" s="5"/>
-    </row>
-    <row r="157" spans="2:2">
-      <c r="B157" s="5"/>
-    </row>
-    <row r="158" spans="2:2">
-      <c r="B158" s="5"/>
-    </row>
-    <row r="159" spans="2:2">
-      <c r="B159" s="5"/>
-    </row>
-    <row r="160" spans="2:2">
-      <c r="B160" s="5"/>
-    </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="5"/>
-    </row>
-    <row r="162" spans="2:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B87" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B88" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B89" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B90" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="B91" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B92" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B93" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B94" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B95" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B96" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="B97" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B98" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B99" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B100" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B101" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="B102" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="B103" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B105" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B107" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="5" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="B109" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="B111" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B212" s="5"/>
     </row>
-    <row r="213" spans="2:2">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B213" s="5"/>
     </row>
-    <row r="214" spans="2:2">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B214" s="5"/>
     </row>
-    <row r="215" spans="2:2">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B215" s="5"/>
     </row>
-    <row r="216" spans="2:2">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B216" s="5"/>
     </row>
-    <row r="217" spans="2:2">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B217" s="5"/>
     </row>
-    <row r="218" spans="2:2">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B218" s="5"/>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B219" s="5"/>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B220" s="5"/>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B221" s="5"/>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B222" s="5"/>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B223" s="5"/>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B224" s="5"/>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B225" s="5"/>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B226" s="5"/>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B227" s="5"/>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B228" s="5"/>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B229" s="5"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:S35">
@@ -3880,1153 +4432,1299 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D81EAC2-667C-41A3-A419-9DF06865FAE0}">
-  <dimension ref="A3:AJ218"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <dimension ref="A3:T218"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" customWidth="1"/>
-    <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="39" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="133.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" style="15" customWidth="1"/>
+    <col min="8" max="8" width="12.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" style="15" customWidth="1"/>
+    <col min="11" max="11" width="12.875" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" style="15" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15" style="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.375" style="15" customWidth="1"/>
+    <col min="22" max="22" width="12" style="15" bestFit="1" customWidth="1"/>
+    <col min="23" max="32" width="13.375" style="15" customWidth="1"/>
+    <col min="33" max="16384" width="8.875" style="15"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-    </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+    </row>
+    <row r="4" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-    </row>
-    <row r="5" spans="1:36">
-      <c r="A5" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="T5" s="6"/>
-    </row>
-    <row r="6" spans="1:36">
-      <c r="A6" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="T5" s="22"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="T6" s="6"/>
-    </row>
-    <row r="7" spans="1:36">
-      <c r="A7" t="s">
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="T6" s="22"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="T7" s="6"/>
-    </row>
-    <row r="8" spans="1:36">
-      <c r="A8" t="s">
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="T7" s="22"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="T8" s="6"/>
-    </row>
-    <row r="9" spans="1:36">
-      <c r="A9" t="s">
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="T8" s="22"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="T9" s="6"/>
-    </row>
-    <row r="10" spans="1:36">
-      <c r="A10" t="s">
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="T9" s="22"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="T10" s="6"/>
-    </row>
-    <row r="11" spans="1:36">
-      <c r="A11" t="s">
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="T10" s="22"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="T11" s="6"/>
-    </row>
-    <row r="12" spans="1:36">
-      <c r="A12" t="s">
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="T11" s="22"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="T12" s="6"/>
-    </row>
-    <row r="13" spans="1:36">
-      <c r="A13" t="s">
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="T12" s="22"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="T13" s="6"/>
-    </row>
-    <row r="14" spans="1:36">
-      <c r="A14" t="s">
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="T13" s="22"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="T14" s="6"/>
-    </row>
-    <row r="15" spans="1:36">
-      <c r="A15" t="s">
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="T14" s="22"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="T15" s="6"/>
-    </row>
-    <row r="16" spans="1:36">
-      <c r="A16" t="s">
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="T15" s="22"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" t="s">
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="P16" s="22"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" t="s">
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="P17" s="22"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" t="s">
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="P18" s="22"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" t="s">
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="P19" s="22"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" t="s">
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="P20" s="22"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" t="s">
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="P21" s="22"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" t="s">
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="P22" s="22"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" t="s">
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="P23" s="22"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" t="s">
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="P24" s="22"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="P25" s="6"/>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" t="s">
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="P25" s="22"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="P26" s="6"/>
-    </row>
-    <row r="27" spans="1:16">
-      <c r="A27" t="s">
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="P26" s="22"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="P27" s="6"/>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="A28" t="s">
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="P27" s="22"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="P28" s="6"/>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="A29" t="s">
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="P28" s="22"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-      <c r="P29" s="6"/>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="A30" t="s">
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="P29" s="22"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-      <c r="P30" s="6"/>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="A31" t="s">
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="P30" s="22"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-      <c r="P31" s="6"/>
-    </row>
-    <row r="32" spans="1:16">
-      <c r="A32" t="s">
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="P31" s="22"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-      <c r="P32" s="6"/>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="A33" t="s">
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="P32" s="22"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="P33" s="6"/>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="A34" t="s">
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="P33" s="22"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="P34" s="6"/>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="A35" t="s">
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="P34" s="22"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-      <c r="P35" s="6"/>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" t="s">
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="P35" s="22"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-      <c r="P36" s="6"/>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" t="s">
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="P36" s="22"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-      <c r="P37" s="6"/>
-    </row>
-    <row r="38" spans="1:16">
-      <c r="A38" t="s">
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="P37" s="22"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-      <c r="P38" s="6"/>
-    </row>
-    <row r="39" spans="1:16">
-      <c r="A39" t="s">
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="P38" s="22"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-      <c r="P39" s="6"/>
-    </row>
-    <row r="40" spans="1:16">
-      <c r="A40" t="s">
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="P39" s="22"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-      <c r="P40" s="6"/>
-    </row>
-    <row r="41" spans="1:16">
-      <c r="A41" t="s">
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="P40" s="22"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-      <c r="P41" s="6"/>
-    </row>
-    <row r="42" spans="1:16">
-      <c r="A42" t="s">
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="P41" s="22"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-      <c r="P42" s="6"/>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" t="s">
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="P42" s="22"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-      <c r="P43" s="6"/>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="A44" t="s">
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="P43" s="22"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-      <c r="P44" s="6"/>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="A45" t="s">
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="P44" s="22"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-      <c r="P45" s="6"/>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" t="s">
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="P45" s="22"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="15" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
-      <c r="A47" t="s">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="15" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
-      <c r="A48" t="s">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A48" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="15" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="15" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="15" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="15" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="15" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="15" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="15" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="15" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="15" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="15" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="15" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="15" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="15" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="15" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="15" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="23" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="15" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="15" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="15" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="15" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="15" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
-      <c r="A70" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="15" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
-      <c r="A71" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="15" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
-      <c r="A72" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="15" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
-      <c r="A73" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="15" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
-      <c r="A74" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="15" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
-      <c r="A75" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="15" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
-      <c r="A76" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="15" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
-      <c r="A77" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="15" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
-      <c r="A78" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="15" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
-      <c r="A79" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="15" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
-      <c r="A80" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="15" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
-      <c r="A81" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="15" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
-      <c r="A82" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="15" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
-      <c r="A83" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="15" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
-      <c r="A84" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="15" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
-      <c r="A85" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="15" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
-      <c r="A86" t="s">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="15" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="151" spans="2:2">
-      <c r="B151" s="5"/>
-    </row>
-    <row r="152" spans="2:2">
-      <c r="B152" s="5"/>
-    </row>
-    <row r="153" spans="2:2">
-      <c r="B153" s="5"/>
-    </row>
-    <row r="154" spans="2:2">
-      <c r="B154" s="5"/>
-    </row>
-    <row r="155" spans="2:2">
-      <c r="B155" s="5"/>
-    </row>
-    <row r="156" spans="2:2">
-      <c r="B156" s="5"/>
-    </row>
-    <row r="157" spans="2:2">
-      <c r="B157" s="5"/>
-    </row>
-    <row r="158" spans="2:2">
-      <c r="B158" s="5"/>
-    </row>
-    <row r="159" spans="2:2">
-      <c r="B159" s="5"/>
-    </row>
-    <row r="160" spans="2:2">
-      <c r="B160" s="5"/>
-    </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="5"/>
-    </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="5"/>
-    </row>
-    <row r="163" spans="2:2">
-      <c r="B163" s="5"/>
-    </row>
-    <row r="164" spans="2:2">
-      <c r="B164" s="5"/>
-    </row>
-    <row r="165" spans="2:2">
-      <c r="B165" s="5"/>
-    </row>
-    <row r="166" spans="2:2">
-      <c r="B166" s="5"/>
-    </row>
-    <row r="167" spans="2:2">
-      <c r="B167" s="5"/>
-    </row>
-    <row r="168" spans="2:2">
-      <c r="B168" s="5"/>
-    </row>
-    <row r="169" spans="2:2">
-      <c r="B169" s="5"/>
-    </row>
-    <row r="170" spans="2:2">
-      <c r="B170" s="5"/>
-    </row>
-    <row r="171" spans="2:2">
-      <c r="B171" s="5"/>
-    </row>
-    <row r="172" spans="2:2">
-      <c r="B172" s="5"/>
-    </row>
-    <row r="173" spans="2:2">
-      <c r="B173" s="5"/>
-    </row>
-    <row r="174" spans="2:2">
-      <c r="B174" s="5"/>
-    </row>
-    <row r="175" spans="2:2">
-      <c r="B175" s="5"/>
-    </row>
-    <row r="176" spans="2:2">
-      <c r="B176" s="5"/>
-    </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="5"/>
-    </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="5"/>
-    </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="5"/>
-    </row>
-    <row r="180" spans="2:2">
-      <c r="B180" s="5"/>
-    </row>
-    <row r="181" spans="2:2">
-      <c r="B181" s="5"/>
-    </row>
-    <row r="182" spans="2:2">
-      <c r="B182" s="5"/>
-    </row>
-    <row r="183" spans="2:2">
-      <c r="B183" s="5"/>
-    </row>
-    <row r="184" spans="2:2">
-      <c r="B184" s="5"/>
-    </row>
-    <row r="185" spans="2:2">
-      <c r="B185" s="5"/>
-    </row>
-    <row r="186" spans="2:2">
-      <c r="B186" s="5"/>
-    </row>
-    <row r="187" spans="2:2">
-      <c r="B187" s="5"/>
-    </row>
-    <row r="188" spans="2:2">
-      <c r="B188" s="5"/>
-    </row>
-    <row r="189" spans="2:2">
-      <c r="B189" s="5"/>
-    </row>
-    <row r="190" spans="2:2">
-      <c r="B190" s="5"/>
-    </row>
-    <row r="191" spans="2:2">
-      <c r="B191" s="5"/>
-    </row>
-    <row r="192" spans="2:2">
-      <c r="B192" s="5"/>
-    </row>
-    <row r="193" spans="2:2">
-      <c r="B193" s="5"/>
-    </row>
-    <row r="194" spans="2:2">
-      <c r="B194" s="5"/>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" s="5"/>
-    </row>
-    <row r="196" spans="2:2">
-      <c r="B196" s="5"/>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" s="5"/>
-    </row>
-    <row r="198" spans="2:2">
-      <c r="B198" s="5"/>
-    </row>
-    <row r="199" spans="2:2">
-      <c r="B199" s="5"/>
-    </row>
-    <row r="200" spans="2:2">
-      <c r="B200" s="5"/>
-    </row>
-    <row r="201" spans="2:2">
-      <c r="B201" s="5"/>
-    </row>
-    <row r="202" spans="2:2">
-      <c r="B202" s="5"/>
-    </row>
-    <row r="203" spans="2:2">
-      <c r="B203" s="5"/>
-    </row>
-    <row r="204" spans="2:2">
-      <c r="B204" s="5"/>
-    </row>
-    <row r="205" spans="2:2">
-      <c r="B205" s="5"/>
-    </row>
-    <row r="206" spans="2:2">
-      <c r="B206" s="5"/>
-    </row>
-    <row r="207" spans="2:2">
-      <c r="B207" s="5"/>
-    </row>
-    <row r="208" spans="2:2">
-      <c r="B208" s="5"/>
-    </row>
-    <row r="209" spans="2:2">
-      <c r="B209" s="5"/>
-    </row>
-    <row r="210" spans="2:2">
-      <c r="B210" s="5"/>
-    </row>
-    <row r="211" spans="2:2">
-      <c r="B211" s="5"/>
-    </row>
-    <row r="212" spans="2:2">
-      <c r="B212" s="5"/>
-    </row>
-    <row r="213" spans="2:2">
-      <c r="B213" s="5"/>
-    </row>
-    <row r="214" spans="2:2">
-      <c r="B214" s="5"/>
-    </row>
-    <row r="215" spans="2:2">
-      <c r="B215" s="5"/>
-    </row>
-    <row r="216" spans="2:2">
-      <c r="B216" s="5"/>
-    </row>
-    <row r="217" spans="2:2">
-      <c r="B217" s="5"/>
-    </row>
-    <row r="218" spans="2:2">
-      <c r="B218" s="5"/>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="21" t="s">
+        <v>446</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A88" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A90" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A92" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="21" t="s">
+        <v>449</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A94" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A96" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A98" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A100" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="B101" s="15" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A102" s="24" t="s">
+        <v>462</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="B103" s="15" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="21" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="21" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="21" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="21" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="B111" s="15" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="21" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B151" s="21"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B152" s="21"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B153" s="21"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B154" s="21"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B155" s="21"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B156" s="21"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B157" s="21"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B158" s="21"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B159" s="21"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B160" s="21"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B161" s="21"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B162" s="21"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B163" s="21"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B164" s="21"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B165" s="21"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B166" s="21"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B167" s="21"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B168" s="21"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B169" s="21"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B170" s="21"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B171" s="21"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B172" s="21"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B173" s="21"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B174" s="21"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B175" s="21"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B176" s="21"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B177" s="21"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B178" s="21"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B179" s="21"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B180" s="21"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B181" s="21"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B182" s="21"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B183" s="21"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B184" s="21"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B185" s="21"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B186" s="21"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B187" s="21"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B188" s="21"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B189" s="21"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B190" s="21"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B191" s="21"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B192" s="21"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B193" s="21"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B194" s="21"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B195" s="21"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B196" s="21"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B197" s="21"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B198" s="21"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B199" s="21"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B200" s="21"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B201" s="21"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B202" s="21"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B203" s="21"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B204" s="21"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B205" s="21"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B206" s="21"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B207" s="21"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B208" s="21"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B209" s="21"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B210" s="21"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B211" s="21"/>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B212" s="21"/>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B213" s="21"/>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B214" s="21"/>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B215" s="21"/>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B216" s="21"/>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B217" s="21"/>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B218" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5068,31 +5766,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB14FF3-77DA-4F15-BE17-E8C413F8CD5E}">
   <dimension ref="A3:AJ218"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.33203125" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>85</v>
       </c>
@@ -5131,7 +5829,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -5161,7 +5859,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -5175,7 +5873,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>169</v>
       </c>
@@ -5189,7 +5887,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>170</v>
       </c>
@@ -5203,7 +5901,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>171</v>
       </c>
@@ -5217,7 +5915,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -5231,7 +5929,7 @@
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>173</v>
       </c>
@@ -5245,7 +5943,7 @@
       <c r="P10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>174</v>
       </c>
@@ -5259,7 +5957,7 @@
       <c r="P11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>175</v>
       </c>
@@ -5273,7 +5971,7 @@
       <c r="P12" s="6"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>176</v>
       </c>
@@ -5287,7 +5985,7 @@
       <c r="P13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>177</v>
       </c>
@@ -5301,7 +5999,7 @@
       <c r="P14" s="6"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>178</v>
       </c>
@@ -5314,7 +6012,7 @@
       <c r="P15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -5323,7 +6021,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>180</v>
       </c>
@@ -5335,7 +6033,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>181</v>
       </c>
@@ -5344,7 +6042,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -5356,7 +6054,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>183</v>
       </c>
@@ -5365,7 +6063,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>184</v>
       </c>
@@ -5377,7 +6075,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>185</v>
       </c>
@@ -5389,7 +6087,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>186</v>
       </c>
@@ -5401,7 +6099,7 @@
       <c r="G23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>187</v>
       </c>
@@ -5410,7 +6108,7 @@
       <c r="G24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>188</v>
       </c>
@@ -5422,7 +6120,7 @@
       <c r="G25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>189</v>
       </c>
@@ -5431,7 +6129,7 @@
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -5443,7 +6141,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>191</v>
       </c>
@@ -5452,7 +6150,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>192</v>
       </c>
@@ -5465,7 +6163,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>193</v>
       </c>
@@ -5478,7 +6176,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>194</v>
       </c>
@@ -5491,7 +6189,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>195</v>
       </c>
@@ -5501,7 +6199,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>196</v>
       </c>
@@ -5513,7 +6211,7 @@
       <c r="G33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -5522,7 +6220,7 @@
       <c r="G34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>198</v>
       </c>
@@ -5535,7 +6233,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>199</v>
       </c>
@@ -5545,7 +6243,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>200</v>
       </c>
@@ -5558,7 +6256,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>201</v>
       </c>
@@ -5571,7 +6269,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>202</v>
       </c>
@@ -5584,7 +6282,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -5594,7 +6292,7 @@
       <c r="H40" s="9"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>204</v>
       </c>
@@ -5607,7 +6305,7 @@
       <c r="H41" s="9"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -5617,7 +6315,7 @@
       <c r="H42" s="9"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>206</v>
       </c>
@@ -5630,7 +6328,7 @@
       <c r="H43" s="9"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>207</v>
       </c>
@@ -5640,215 +6338,215 @@
       <c r="H44" s="9"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="151" spans="2:2">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B212" s="5"/>
     </row>
-    <row r="213" spans="2:2">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B213" s="5"/>
     </row>
-    <row r="214" spans="2:2">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B214" s="5"/>
     </row>
-    <row r="215" spans="2:2">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B215" s="5"/>
     </row>
-    <row r="216" spans="2:2">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B216" s="5"/>
     </row>
-    <row r="217" spans="2:2">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B217" s="5"/>
     </row>
-    <row r="218" spans="2:2">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B218" s="5"/>
     </row>
   </sheetData>
@@ -5891,31 +6589,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC7F4074-9E65-434B-897B-FD6EE64CA765}">
   <dimension ref="A3:AJ218"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.33203125" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>237</v>
       </c>
@@ -5954,7 +6652,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -5984,7 +6682,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -5998,7 +6696,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>169</v>
       </c>
@@ -6012,7 +6710,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>170</v>
       </c>
@@ -6026,7 +6724,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>171</v>
       </c>
@@ -6037,7 +6735,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -6051,7 +6749,7 @@
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>173</v>
       </c>
@@ -6062,7 +6760,7 @@
       <c r="P10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>174</v>
       </c>
@@ -6076,7 +6774,7 @@
       <c r="P11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>175</v>
       </c>
@@ -6087,7 +6785,7 @@
       <c r="P12" s="6"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>176</v>
       </c>
@@ -6101,7 +6799,7 @@
       <c r="P13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>177</v>
       </c>
@@ -6115,7 +6813,7 @@
       <c r="P14" s="6"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>178</v>
       </c>
@@ -6128,7 +6826,7 @@
       <c r="P15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -6137,7 +6835,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>180</v>
       </c>
@@ -6149,7 +6847,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>181</v>
       </c>
@@ -6158,7 +6856,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -6170,7 +6868,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>183</v>
       </c>
@@ -6179,7 +6877,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>184</v>
       </c>
@@ -6191,7 +6889,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>185</v>
       </c>
@@ -6203,7 +6901,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>186</v>
       </c>
@@ -6215,7 +6913,7 @@
       <c r="G23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>187</v>
       </c>
@@ -6224,7 +6922,7 @@
       <c r="G24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>188</v>
       </c>
@@ -6236,7 +6934,7 @@
       <c r="G25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>189</v>
       </c>
@@ -6245,7 +6943,7 @@
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -6257,7 +6955,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>191</v>
       </c>
@@ -6266,7 +6964,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>192</v>
       </c>
@@ -6279,7 +6977,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>193</v>
       </c>
@@ -6292,7 +6990,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>194</v>
       </c>
@@ -6305,7 +7003,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>195</v>
       </c>
@@ -6315,7 +7013,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>196</v>
       </c>
@@ -6327,7 +7025,7 @@
       <c r="G33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -6336,7 +7034,7 @@
       <c r="G34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>198</v>
       </c>
@@ -6349,7 +7047,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>199</v>
       </c>
@@ -6359,7 +7057,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>200</v>
       </c>
@@ -6372,7 +7070,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>201</v>
       </c>
@@ -6385,7 +7083,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>202</v>
       </c>
@@ -6398,7 +7096,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -6408,7 +7106,7 @@
       <c r="H40" s="9"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>204</v>
       </c>
@@ -6421,7 +7119,7 @@
       <c r="H41" s="9"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -6431,7 +7129,7 @@
       <c r="H42" s="9"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>206</v>
       </c>
@@ -6444,7 +7142,7 @@
       <c r="H43" s="9"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>207</v>
       </c>
@@ -6454,215 +7152,215 @@
       <c r="H44" s="9"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="151" spans="2:2">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B212" s="5"/>
     </row>
-    <row r="213" spans="2:2">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B213" s="5"/>
     </row>
-    <row r="214" spans="2:2">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B214" s="5"/>
     </row>
-    <row r="215" spans="2:2">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B215" s="5"/>
     </row>
-    <row r="216" spans="2:2">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B216" s="5"/>
     </row>
-    <row r="217" spans="2:2">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B217" s="5"/>
     </row>
-    <row r="218" spans="2:2">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B218" s="5"/>
     </row>
   </sheetData>
@@ -6704,32 +7402,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1DEF80-1767-4678-9A0F-3D65DA9959F4}">
-  <dimension ref="A3:AJ212"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <dimension ref="A3:AJ202"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.33203125" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>343</v>
       </c>
@@ -6768,7 +7466,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -6798,7 +7496,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>345</v>
       </c>
@@ -6812,7 +7510,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>346</v>
       </c>
@@ -6826,7 +7524,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>351</v>
       </c>
@@ -6839,7 +7537,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>375</v>
       </c>
@@ -6852,7 +7550,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>353</v>
       </c>
@@ -6864,7 +7562,7 @@
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>354</v>
       </c>
@@ -6876,7 +7574,7 @@
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>355</v>
       </c>
@@ -6888,7 +7586,7 @@
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>356</v>
       </c>
@@ -6900,7 +7598,7 @@
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>357</v>
       </c>
@@ -6912,7 +7610,7 @@
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>338</v>
       </c>
@@ -6924,7 +7622,7 @@
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>358</v>
       </c>
@@ -6936,7 +7634,7 @@
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>436</v>
       </c>
@@ -6948,7 +7646,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>359</v>
       </c>
@@ -6960,7 +7658,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>377</v>
       </c>
@@ -6972,7 +7670,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>379</v>
       </c>
@@ -6984,7 +7682,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>381</v>
       </c>
@@ -6996,7 +7694,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>383</v>
       </c>
@@ -7008,7 +7706,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>385</v>
       </c>
@@ -7020,7 +7718,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>387</v>
       </c>
@@ -7033,7 +7731,7 @@
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>389</v>
       </c>
@@ -7046,7 +7744,7 @@
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>391</v>
       </c>
@@ -7059,7 +7757,7 @@
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>393</v>
       </c>
@@ -7072,7 +7770,7 @@
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>395</v>
       </c>
@@ -7084,7 +7782,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>396</v>
       </c>
@@ -7096,7 +7794,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>397</v>
       </c>
@@ -7109,7 +7807,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>398</v>
       </c>
@@ -7122,7 +7820,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>399</v>
       </c>
@@ -7135,7 +7833,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>400</v>
       </c>
@@ -7148,7 +7846,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>401</v>
       </c>
@@ -7161,7 +7859,7 @@
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>412</v>
       </c>
@@ -7174,7 +7872,7 @@
       <c r="H34" s="9"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>415</v>
       </c>
@@ -7187,7 +7885,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>419</v>
       </c>
@@ -7200,7 +7898,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>420</v>
       </c>
@@ -7213,7 +7911,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>421</v>
       </c>
@@ -7226,7 +7924,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>422</v>
       </c>
@@ -7239,7 +7937,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>430</v>
       </c>
@@ -7247,7 +7945,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>432</v>
       </c>
@@ -7255,209 +7953,241 @@
         <v>435</v>
       </c>
     </row>
-    <row r="145" spans="2:2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>437</v>
+      </c>
+      <c r="B42" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>508</v>
+      </c>
+      <c r="B43" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>511</v>
+      </c>
+      <c r="B44" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>513</v>
+      </c>
+      <c r="B45" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B135" s="5"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B136" s="5"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B137" s="5"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B138" s="5"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B139" s="5"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B140" s="5"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B141" s="5"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B142" s="5"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B143" s="5"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B144" s="5"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B202" s="5"/>
-    </row>
-    <row r="203" spans="2:2">
-      <c r="B203" s="5"/>
-    </row>
-    <row r="204" spans="2:2">
-      <c r="B204" s="5"/>
-    </row>
-    <row r="205" spans="2:2">
-      <c r="B205" s="5"/>
-    </row>
-    <row r="206" spans="2:2">
-      <c r="B206" s="5"/>
-    </row>
-    <row r="207" spans="2:2">
-      <c r="B207" s="5"/>
-    </row>
-    <row r="208" spans="2:2">
-      <c r="B208" s="5"/>
-    </row>
-    <row r="209" spans="2:2">
-      <c r="B209" s="5"/>
-    </row>
-    <row r="210" spans="2:2">
-      <c r="B210" s="5"/>
-    </row>
-    <row r="211" spans="2:2">
-      <c r="B211" s="5"/>
-    </row>
-    <row r="212" spans="2:2">
-      <c r="B212" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7498,32 +8228,32 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448EFE5B-7539-4545-AC12-95181FCEF528}">
-  <dimension ref="A3:AJ206"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <dimension ref="A3:AJ197"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.33203125" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>344</v>
       </c>
@@ -7562,7 +8292,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -7592,7 +8322,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>345</v>
       </c>
@@ -7604,7 +8334,7 @@
       <c r="G5" s="6"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>346</v>
       </c>
@@ -7616,7 +8346,7 @@
       <c r="G6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>351</v>
       </c>
@@ -7628,7 +8358,7 @@
       <c r="G7" s="6"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>375</v>
       </c>
@@ -7640,7 +8370,7 @@
       <c r="G8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>353</v>
       </c>
@@ -7652,7 +8382,7 @@
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>354</v>
       </c>
@@ -7664,7 +8394,7 @@
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>355</v>
       </c>
@@ -7676,7 +8406,7 @@
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>356</v>
       </c>
@@ -7688,7 +8418,7 @@
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>357</v>
       </c>
@@ -7700,7 +8430,7 @@
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>338</v>
       </c>
@@ -7712,7 +8442,7 @@
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>358</v>
       </c>
@@ -7724,7 +8454,7 @@
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>436</v>
       </c>
@@ -7736,7 +8466,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>359</v>
       </c>
@@ -7749,7 +8479,7 @@
       <c r="H17" s="9"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>377</v>
       </c>
@@ -7762,7 +8492,7 @@
       <c r="H18" s="9"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>379</v>
       </c>
@@ -7775,7 +8505,7 @@
       <c r="H19" s="9"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>381</v>
       </c>
@@ -7788,7 +8518,7 @@
       <c r="H20" s="9"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>383</v>
       </c>
@@ -7800,7 +8530,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>385</v>
       </c>
@@ -7812,7 +8542,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>387</v>
       </c>
@@ -7825,7 +8555,7 @@
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>389</v>
       </c>
@@ -7838,7 +8568,7 @@
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>391</v>
       </c>
@@ -7851,7 +8581,7 @@
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>393</v>
       </c>
@@ -7864,7 +8594,7 @@
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>395</v>
       </c>
@@ -7877,7 +8607,7 @@
       <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>396</v>
       </c>
@@ -7890,7 +8620,7 @@
       <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>397</v>
       </c>
@@ -7903,7 +8633,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>398</v>
       </c>
@@ -7916,7 +8646,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>399</v>
       </c>
@@ -7929,7 +8659,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>400</v>
       </c>
@@ -7942,7 +8672,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>401</v>
       </c>
@@ -7955,7 +8685,7 @@
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>412</v>
       </c>
@@ -7963,7 +8693,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>414</v>
       </c>
@@ -7971,7 +8701,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>419</v>
       </c>
@@ -7979,7 +8709,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>420</v>
       </c>
@@ -7987,7 +8717,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>421</v>
       </c>
@@ -7995,7 +8725,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>422</v>
       </c>
@@ -8003,7 +8733,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>430</v>
       </c>
@@ -8011,7 +8741,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>432</v>
       </c>
@@ -8019,289 +8749,241 @@
         <v>433</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>353</v>
+        <v>437</v>
       </c>
       <c r="B42" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>354</v>
+        <v>508</v>
       </c>
       <c r="B43" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>355</v>
+        <v>511</v>
       </c>
       <c r="B44" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>356</v>
+        <v>513</v>
       </c>
       <c r="B45" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" t="s">
-        <v>357</v>
-      </c>
-      <c r="B46" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="A47" t="s">
-        <v>338</v>
-      </c>
-      <c r="B47" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="A48" t="s">
-        <v>358</v>
-      </c>
-      <c r="B48" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>359</v>
-      </c>
-      <c r="B49" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>436</v>
-      </c>
-      <c r="B50" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>437</v>
-      </c>
-      <c r="B51" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="139" spans="2:2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B130" s="5"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B131" s="5"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B132" s="5"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B133" s="5"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B134" s="5"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B135" s="5"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B136" s="5"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B137" s="5"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B138" s="5"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B139" s="5"/>
     </row>
-    <row r="140" spans="2:2">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B140" s="5"/>
     </row>
-    <row r="141" spans="2:2">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B141" s="5"/>
     </row>
-    <row r="142" spans="2:2">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B142" s="5"/>
     </row>
-    <row r="143" spans="2:2">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B143" s="5"/>
     </row>
-    <row r="144" spans="2:2">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B144" s="5"/>
     </row>
-    <row r="145" spans="2:2">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="5"/>
-    </row>
-    <row r="198" spans="2:2">
-      <c r="B198" s="5"/>
-    </row>
-    <row r="199" spans="2:2">
-      <c r="B199" s="5"/>
-    </row>
-    <row r="200" spans="2:2">
-      <c r="B200" s="5"/>
-    </row>
-    <row r="201" spans="2:2">
-      <c r="B201" s="5"/>
-    </row>
-    <row r="202" spans="2:2">
-      <c r="B202" s="5"/>
-    </row>
-    <row r="203" spans="2:2">
-      <c r="B203" s="5"/>
-    </row>
-    <row r="204" spans="2:2">
-      <c r="B204" s="5"/>
-    </row>
-    <row r="205" spans="2:2">
-      <c r="B205" s="5"/>
-    </row>
-    <row r="206" spans="2:2">
-      <c r="B206" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8343,31 +9025,31 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D9F6-C7CE-4D6D-A307-34F0A02C664A}">
   <dimension ref="A3:AJ212"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.33203125" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>367</v>
       </c>
@@ -8406,7 +9088,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -8436,7 +9118,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>369</v>
       </c>
@@ -8450,7 +9132,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>370</v>
       </c>
@@ -8464,7 +9146,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -8472,7 +9154,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -8480,410 +9162,410 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="5:16">
+    <row r="17" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="5:16">
+    <row r="18" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="5:16">
+    <row r="19" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="5:16">
+    <row r="20" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="5:16">
+    <row r="21" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="5:16">
+    <row r="22" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="5:16">
+    <row r="23" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="5:16">
+    <row r="24" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="5:16">
+    <row r="25" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="5:16">
+    <row r="26" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="5:16">
+    <row r="27" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="5:16">
+    <row r="28" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="5:16">
+    <row r="29" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="5:16">
+    <row r="30" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="5:16">
+    <row r="31" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="5:16">
+    <row r="32" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="5:16">
+    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="5:16">
+    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="5:16">
+    <row r="35" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="5:16">
+    <row r="36" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="5:16">
+    <row r="37" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="5:16">
+    <row r="38" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="5:16">
+    <row r="39" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="145" spans="2:2">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B212" s="5"/>
     </row>
   </sheetData>
@@ -8926,31 +9608,31 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC371501-4D80-4BA3-AE38-ACD1D9A5C0BD}">
   <dimension ref="A3:AJ206"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="21" max="21" width="13.375" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.33203125" customWidth="1"/>
+    <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>368</v>
       </c>
@@ -8989,7 +9671,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -9019,7 +9701,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>369</v>
       </c>
@@ -9031,7 +9713,7 @@
       <c r="G5" s="6"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>370</v>
       </c>
@@ -9043,128 +9725,128 @@
       <c r="G6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="2:16">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="2:16">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="2:16">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="2:16">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="2:16">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="2:16">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="2:16">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="2:16">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="2:16">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="2:16">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="9"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -9172,257 +9854,257 @@
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="2:16">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="2:16">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="2:16">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="2:16">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="2:16">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="2:16">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="5:16">
+    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="139" spans="2:2">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B139" s="5"/>
     </row>
-    <row r="140" spans="2:2">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B140" s="5"/>
     </row>
-    <row r="141" spans="2:2">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B141" s="5"/>
     </row>
-    <row r="142" spans="2:2">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B142" s="5"/>
     </row>
-    <row r="143" spans="2:2">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B143" s="5"/>
     </row>
-    <row r="144" spans="2:2">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B144" s="5"/>
     </row>
-    <row r="145" spans="2:2">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B206" s="5"/>
     </row>
   </sheetData>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE86E66-0E20-4056-976C-C5E37AA46FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E616ED17-2B1F-43D5-85D1-9ED4B3F2CC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="15150" windowHeight="15585" firstSheet="2" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="536">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1904,12 +1904,92 @@
     <t>Food</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Money</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExitGame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 종료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이틀 메뉴로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExitToTitle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exit To Title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exit Game</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MasterVolume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MusicVolume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AmbientVolume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사운드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 볼륨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음악 볼륨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주변음 볼륨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Master Volume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Music Volume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ambient Volume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2027,7 +2107,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2064,9 +2144,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2098,9 +2175,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3044,7 +3118,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB82EE84-0108-42B1-826D-C63A5B94B9EE}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A3:AJ229"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="131.25" bestFit="1" customWidth="1"/>
@@ -3068,7 +3142,7 @@
     <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -3107,7 +3181,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -3137,7 +3211,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -3151,7 +3225,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -3165,7 +3239,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -3179,7 +3253,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -3193,7 +3267,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -3207,7 +3281,7 @@
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -3221,7 +3295,7 @@
       <c r="P10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>92</v>
       </c>
@@ -3235,7 +3309,7 @@
       <c r="P11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -3249,7 +3323,7 @@
       <c r="P12" s="6"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -3263,7 +3337,7 @@
       <c r="P13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>95</v>
       </c>
@@ -3277,7 +3351,7 @@
       <c r="P14" s="6"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -3290,7 +3364,7 @@
       <c r="P15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -3302,7 +3376,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -3314,7 +3388,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>99</v>
       </c>
@@ -3326,7 +3400,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -3338,7 +3412,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>101</v>
       </c>
@@ -3350,7 +3424,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -3362,7 +3436,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -3374,7 +3448,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -3386,7 +3460,7 @@
       <c r="G23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -3398,7 +3472,7 @@
       <c r="G24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -3410,7 +3484,7 @@
       <c r="G25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -3422,7 +3496,7 @@
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -3434,7 +3508,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>109</v>
       </c>
@@ -3446,7 +3520,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -3459,7 +3533,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -3472,7 +3546,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -3485,7 +3559,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -3498,7 +3572,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>114</v>
       </c>
@@ -3510,7 +3584,7 @@
       <c r="G33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>115</v>
       </c>
@@ -3522,7 +3596,7 @@
       <c r="G34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>116</v>
       </c>
@@ -3535,7 +3609,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>117</v>
       </c>
@@ -3548,7 +3622,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -3561,7 +3635,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>119</v>
       </c>
@@ -3574,7 +3648,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>120</v>
       </c>
@@ -3587,7 +3661,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>121</v>
       </c>
@@ -3600,7 +3674,7 @@
       <c r="H40" s="9"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>122</v>
       </c>
@@ -3613,7 +3687,7 @@
       <c r="H41" s="9"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -3626,7 +3700,7 @@
       <c r="H42" s="9"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>124</v>
       </c>
@@ -3639,7 +3713,7 @@
       <c r="H43" s="9"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>125</v>
       </c>
@@ -3652,7 +3726,7 @@
       <c r="H44" s="9"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>126</v>
       </c>
@@ -3665,7 +3739,7 @@
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>127</v>
       </c>
@@ -3673,7 +3747,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>128</v>
       </c>
@@ -3681,7 +3755,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>129</v>
       </c>
@@ -3689,7 +3763,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>130</v>
       </c>
@@ -3697,7 +3771,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>131</v>
       </c>
@@ -3705,7 +3779,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>132</v>
       </c>
@@ -3713,7 +3787,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>133</v>
       </c>
@@ -3721,7 +3795,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>134</v>
       </c>
@@ -3729,7 +3803,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>135</v>
       </c>
@@ -3737,7 +3811,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>136</v>
       </c>
@@ -3745,7 +3819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>137</v>
       </c>
@@ -3753,7 +3827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>138</v>
       </c>
@@ -3761,7 +3835,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>139</v>
       </c>
@@ -3769,7 +3843,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>140</v>
       </c>
@@ -3777,7 +3851,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>141</v>
       </c>
@@ -3785,7 +3859,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>142</v>
       </c>
@@ -3793,7 +3867,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>143</v>
       </c>
@@ -3801,7 +3875,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>144</v>
       </c>
@@ -3809,7 +3883,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>145</v>
       </c>
@@ -3817,7 +3891,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>146</v>
       </c>
@@ -3825,7 +3899,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>147</v>
       </c>
@@ -3833,7 +3907,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>148</v>
       </c>
@@ -3841,7 +3915,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>149</v>
       </c>
@@ -3849,7 +3923,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>150</v>
       </c>
@@ -3857,7 +3931,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>151</v>
       </c>
@@ -3865,7 +3939,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -3873,7 +3947,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>153</v>
       </c>
@@ -3881,7 +3955,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>154</v>
       </c>
@@ -3889,7 +3963,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>155</v>
       </c>
@@ -3897,7 +3971,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>156</v>
       </c>
@@ -3905,7 +3979,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>157</v>
       </c>
@@ -3913,7 +3987,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>158</v>
       </c>
@@ -3921,7 +3995,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>159</v>
       </c>
@@ -3929,7 +4003,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>160</v>
       </c>
@@ -3937,7 +4011,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2">
       <c r="A80" t="s">
         <v>161</v>
       </c>
@@ -3945,7 +4019,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>162</v>
       </c>
@@ -3953,7 +4027,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -3961,7 +4035,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>164</v>
       </c>
@@ -3969,7 +4043,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>165</v>
       </c>
@@ -3977,7 +4051,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>166</v>
       </c>
@@ -3985,7 +4059,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
         <v>454</v>
       </c>
@@ -3993,7 +4067,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2">
       <c r="A87" s="5" t="s">
         <v>446</v>
       </c>
@@ -4001,7 +4075,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2">
       <c r="A88" s="5" t="s">
         <v>455</v>
       </c>
@@ -4009,7 +4083,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2">
       <c r="A89" s="5" t="s">
         <v>447</v>
       </c>
@@ -4017,7 +4091,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2">
       <c r="A90" s="5" t="s">
         <v>456</v>
       </c>
@@ -4025,7 +4099,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
         <v>448</v>
       </c>
@@ -4033,7 +4107,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2">
       <c r="A92" s="5" t="s">
         <v>457</v>
       </c>
@@ -4041,7 +4115,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2">
       <c r="A93" s="5" t="s">
         <v>449</v>
       </c>
@@ -4049,7 +4123,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2">
       <c r="A94" s="5" t="s">
         <v>458</v>
       </c>
@@ -4057,7 +4131,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
         <v>450</v>
       </c>
@@ -4065,7 +4139,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2">
       <c r="A96" s="5" t="s">
         <v>459</v>
       </c>
@@ -4073,7 +4147,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
         <v>451</v>
       </c>
@@ -4081,7 +4155,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2">
       <c r="A98" s="5" t="s">
         <v>460</v>
       </c>
@@ -4089,7 +4163,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2">
       <c r="A99" s="5" t="s">
         <v>452</v>
       </c>
@@ -4097,7 +4171,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2">
       <c r="A100" s="5" t="s">
         <v>461</v>
       </c>
@@ -4105,7 +4179,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2">
       <c r="A101" s="5" t="s">
         <v>453</v>
       </c>
@@ -4113,15 +4187,15 @@
         <v>477</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" s="12" t="s">
+    <row r="102" spans="1:2">
+      <c r="A102" s="5" t="s">
         <v>462</v>
       </c>
       <c r="B102" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2">
       <c r="A103" s="5" t="s">
         <v>488</v>
       </c>
@@ -4129,12 +4203,12 @@
         <v>490</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2">
       <c r="A104" s="5" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2">
       <c r="A105" s="5" t="s">
         <v>480</v>
       </c>
@@ -4142,12 +4216,12 @@
         <v>491</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2">
       <c r="A106" s="5" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2">
       <c r="A107" s="5" t="s">
         <v>481</v>
       </c>
@@ -4155,12 +4229,12 @@
         <v>492</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2">
       <c r="A108" s="5" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2">
       <c r="A109" s="5" t="s">
         <v>482</v>
       </c>
@@ -4168,12 +4242,12 @@
         <v>493</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2">
       <c r="A110" s="5" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2">
       <c r="A111" s="5" t="s">
         <v>483</v>
       </c>
@@ -4181,213 +4255,213 @@
         <v>494</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2">
       <c r="A112" s="5" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:2">
       <c r="B212" s="5"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:2">
       <c r="B213" s="5"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:2">
       <c r="B214" s="5"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:2">
       <c r="B215" s="5"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:2">
       <c r="B216" s="5"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:2">
       <c r="B217" s="5"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:2">
       <c r="B218" s="5"/>
     </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:2">
       <c r="B219" s="5"/>
     </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:2">
       <c r="B220" s="5"/>
     </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:2">
       <c r="B221" s="5"/>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:2">
       <c r="B222" s="5"/>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:2">
       <c r="B223" s="5"/>
     </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:2">
       <c r="B224" s="5"/>
     </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:2">
       <c r="B225" s="5"/>
     </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:2">
       <c r="B226" s="5"/>
     </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:2">
       <c r="B227" s="5"/>
     </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:2">
       <c r="B228" s="5"/>
     </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:2">
       <c r="B229" s="5"/>
     </row>
   </sheetData>
@@ -4433,1298 +4507,1298 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D81EAC2-667C-41A3-A419-9DF06865FAE0}">
   <dimension ref="A3:T218"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="39" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="133.5" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="12.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.375" style="15" customWidth="1"/>
-    <col min="11" max="11" width="12.875" style="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" style="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.375" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.625" style="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.625" style="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15" style="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.375" style="15" customWidth="1"/>
-    <col min="22" max="22" width="12" style="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="13.375" style="15" customWidth="1"/>
-    <col min="33" max="16384" width="8.875" style="15"/>
+    <col min="1" max="1" width="39" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="133.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="12.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.375" style="14" customWidth="1"/>
+    <col min="11" max="11" width="12.875" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.625" style="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" style="14" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.625" style="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.375" style="14" customWidth="1"/>
+    <col min="22" max="22" width="12" style="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="32" width="13.375" style="14" customWidth="1"/>
+    <col min="33" max="16384" width="8.875" style="14"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A3" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-    </row>
-    <row r="4" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="T5" s="22"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="T5" s="21"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="T6" s="22"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="T6" s="21"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="T7" s="22"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="T7" s="21"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="T8" s="22"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="T8" s="21"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="T9" s="22"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="T9" s="21"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="T10" s="22"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="T10" s="21"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="T11" s="22"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="T11" s="21"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="T12" s="22"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="T12" s="21"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="T13" s="22"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="T13" s="21"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="T14" s="22"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="T14" s="21"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="T15" s="22"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="T15" s="21"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="P16" s="22"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="P16" s="21"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="P17" s="22"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="P17" s="21"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="P18" s="22"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="P18" s="21"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="P19" s="22"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="P19" s="21"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="P20" s="22"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="P20" s="21"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="P21" s="22"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="P21" s="21"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="P22" s="22"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="P22" s="21"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="P23" s="22"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="P23" s="21"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="P24" s="22"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="P24" s="21"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="P25" s="22"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="P25" s="21"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="P26" s="22"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="P26" s="21"/>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="P27" s="22"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="P27" s="21"/>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="P28" s="22"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="P28" s="21"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="P29" s="22"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="P29" s="21"/>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="P30" s="22"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="P30" s="21"/>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="P31" s="22"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="P31" s="21"/>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="P32" s="22"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="P32" s="21"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="P33" s="22"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="P33" s="21"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="P34" s="22"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" s="15" t="s">
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="P34" s="21"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="P35" s="22"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="15" t="s">
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="P35" s="21"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="P36" s="22"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="P36" s="21"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="P37" s="22"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="P37" s="21"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="P38" s="22"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A39" s="15" t="s">
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="P38" s="21"/>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="P39" s="22"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" s="15" t="s">
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="P39" s="21"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="P40" s="22"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A41" s="15" t="s">
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="P40" s="21"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="P41" s="22"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A42" s="15" t="s">
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="P41" s="21"/>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="P42" s="22"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="15" t="s">
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="P42" s="21"/>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="P43" s="22"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="P43" s="21"/>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="P44" s="22"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="P44" s="21"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="P45" s="22"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="P45" s="21"/>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="14" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
+    <row r="47" spans="1:16">
+      <c r="A47" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="14" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
+    <row r="48" spans="1:16">
+      <c r="A48" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="14" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="15" t="s">
+    <row r="49" spans="1:2">
+      <c r="A49" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="14" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="15" t="s">
+    <row r="50" spans="1:2">
+      <c r="A50" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="14" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="15" t="s">
+    <row r="51" spans="1:2">
+      <c r="A51" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="14" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="15" t="s">
+    <row r="52" spans="1:2">
+      <c r="A52" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="14" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="15" t="s">
+    <row r="53" spans="1:2">
+      <c r="A53" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="14" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="15" t="s">
+    <row r="54" spans="1:2">
+      <c r="A54" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="15" t="s">
+    <row r="55" spans="1:2">
+      <c r="A55" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="14" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="15" t="s">
+    <row r="56" spans="1:2">
+      <c r="A56" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="14" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="15" t="s">
+    <row r="57" spans="1:2">
+      <c r="A57" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="14" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="15" t="s">
+    <row r="58" spans="1:2">
+      <c r="A58" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="14" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="15" t="s">
+    <row r="59" spans="1:2">
+      <c r="A59" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="14" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="15" t="s">
+    <row r="60" spans="1:2">
+      <c r="A60" s="14" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="15" t="s">
+    <row r="61" spans="1:2">
+      <c r="A61" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="14" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="15" t="s">
+    <row r="62" spans="1:2">
+      <c r="A62" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="14" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="15" t="s">
+    <row r="63" spans="1:2">
+      <c r="A63" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="14" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="15" t="s">
+    <row r="64" spans="1:2">
+      <c r="A64" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="B64" s="22" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="15" t="s">
+    <row r="65" spans="1:2">
+      <c r="A65" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="14" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="15" t="s">
+    <row r="66" spans="1:2">
+      <c r="A66" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="14" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="15" t="s">
+    <row r="67" spans="1:2">
+      <c r="A67" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="14" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="15" t="s">
+    <row r="68" spans="1:2">
+      <c r="A68" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="14" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="15" t="s">
+    <row r="69" spans="1:2">
+      <c r="A69" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="14" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="15" t="s">
+    <row r="70" spans="1:2">
+      <c r="A70" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="14" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="15" t="s">
+    <row r="71" spans="1:2">
+      <c r="A71" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="14" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="15" t="s">
+    <row r="72" spans="1:2">
+      <c r="A72" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="14" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="15" t="s">
+    <row r="73" spans="1:2">
+      <c r="A73" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="14" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="15" t="s">
+    <row r="74" spans="1:2">
+      <c r="A74" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="14" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="15" t="s">
+    <row r="75" spans="1:2">
+      <c r="A75" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="14" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="15" t="s">
+    <row r="76" spans="1:2">
+      <c r="A76" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="B76" s="15" t="s">
+      <c r="B76" s="14" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="15" t="s">
+    <row r="77" spans="1:2">
+      <c r="A77" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" s="14" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="15" t="s">
+    <row r="78" spans="1:2">
+      <c r="A78" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="14" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="15" t="s">
+    <row r="79" spans="1:2">
+      <c r="A79" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" s="14" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="15" t="s">
+    <row r="80" spans="1:2">
+      <c r="A80" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="B80" s="15" t="s">
+      <c r="B80" s="14" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="15" t="s">
+    <row r="81" spans="1:2">
+      <c r="A81" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" s="14" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="15" t="s">
+    <row r="82" spans="1:2">
+      <c r="A82" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="14" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="15" t="s">
+    <row r="83" spans="1:2">
+      <c r="A83" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B83" s="14" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="15" t="s">
+    <row r="84" spans="1:2">
+      <c r="A84" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B84" s="15" t="s">
+      <c r="B84" s="14" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="15" t="s">
+    <row r="85" spans="1:2">
+      <c r="A85" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" s="14" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="15" t="s">
+    <row r="86" spans="1:2">
+      <c r="A86" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="14" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="21" t="s">
+    <row r="87" spans="1:2">
+      <c r="A87" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="14" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A88" s="21" t="s">
+    <row r="88" spans="1:2" ht="17.25">
+      <c r="A88" s="20" t="s">
         <v>455</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="12" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" s="21" t="s">
+    <row r="89" spans="1:2">
+      <c r="A89" s="20" t="s">
         <v>447</v>
       </c>
-      <c r="B89" s="15" t="s">
+      <c r="B89" s="14" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A90" s="21" t="s">
+    <row r="90" spans="1:2" ht="17.25">
+      <c r="A90" s="20" t="s">
         <v>456</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="12" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="21" t="s">
+    <row r="91" spans="1:2">
+      <c r="A91" s="20" t="s">
         <v>448</v>
       </c>
-      <c r="B91" s="15" t="s">
+      <c r="B91" s="14" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A92" s="21" t="s">
+    <row r="92" spans="1:2" ht="17.25">
+      <c r="A92" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="12" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="21" t="s">
+    <row r="93" spans="1:2">
+      <c r="A93" s="20" t="s">
         <v>449</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B93" s="14" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A94" s="21" t="s">
+    <row r="94" spans="1:2" ht="17.25">
+      <c r="A94" s="20" t="s">
         <v>458</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="12" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" s="21" t="s">
+    <row r="95" spans="1:2">
+      <c r="A95" s="20" t="s">
         <v>450</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" s="14" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A96" s="21" t="s">
+    <row r="96" spans="1:2" ht="17.25">
+      <c r="A96" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="12" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="21" t="s">
+    <row r="97" spans="1:2">
+      <c r="A97" s="20" t="s">
         <v>451</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="14" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A98" s="21" t="s">
+    <row r="98" spans="1:2" ht="17.25">
+      <c r="A98" s="20" t="s">
         <v>460</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="12" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" s="21" t="s">
+    <row r="99" spans="1:2">
+      <c r="A99" s="20" t="s">
         <v>452</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="14" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A100" s="21" t="s">
+    <row r="100" spans="1:2" ht="17.25">
+      <c r="A100" s="20" t="s">
         <v>461</v>
       </c>
-      <c r="B100" s="13" t="s">
+      <c r="B100" s="12" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="21" t="s">
+    <row r="101" spans="1:2">
+      <c r="A101" s="20" t="s">
         <v>453</v>
       </c>
-      <c r="B101" s="15" t="s">
+      <c r="B101" s="14" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A102" s="24" t="s">
+    <row r="102" spans="1:2" ht="17.25">
+      <c r="A102" s="20" t="s">
         <v>462</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" s="12" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" s="21" t="s">
+    <row r="103" spans="1:2">
+      <c r="A103" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" s="14" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" s="21" t="s">
+    <row r="104" spans="1:2">
+      <c r="A104" s="20" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" s="21" t="s">
+    <row r="105" spans="1:2">
+      <c r="A105" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="B105" s="15" t="s">
+      <c r="B105" s="14" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" s="21" t="s">
+    <row r="106" spans="1:2">
+      <c r="A106" s="20" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" s="21" t="s">
+    <row r="107" spans="1:2">
+      <c r="A107" s="20" t="s">
         <v>481</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="14" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" s="21" t="s">
+    <row r="108" spans="1:2">
+      <c r="A108" s="20" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" s="21" t="s">
+    <row r="109" spans="1:2">
+      <c r="A109" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="B109" s="15" t="s">
+      <c r="B109" s="14" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110" s="21" t="s">
+    <row r="110" spans="1:2">
+      <c r="A110" s="20" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111" s="21" t="s">
+    <row r="111" spans="1:2">
+      <c r="A111" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" s="14" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112" s="21" t="s">
+    <row r="112" spans="1:2">
+      <c r="A112" s="20" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B151" s="21"/>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B152" s="21"/>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B153" s="21"/>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B154" s="21"/>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B155" s="21"/>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B156" s="21"/>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B157" s="21"/>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B158" s="21"/>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B159" s="21"/>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B160" s="21"/>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B161" s="21"/>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B162" s="21"/>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B163" s="21"/>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B164" s="21"/>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B165" s="21"/>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B166" s="21"/>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B167" s="21"/>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B168" s="21"/>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B169" s="21"/>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B170" s="21"/>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B171" s="21"/>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B172" s="21"/>
-    </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B173" s="21"/>
-    </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B174" s="21"/>
-    </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B175" s="21"/>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B176" s="21"/>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B177" s="21"/>
-    </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B178" s="21"/>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B179" s="21"/>
-    </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B180" s="21"/>
-    </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B181" s="21"/>
-    </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B182" s="21"/>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B183" s="21"/>
-    </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B184" s="21"/>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B185" s="21"/>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B186" s="21"/>
-    </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B187" s="21"/>
-    </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B188" s="21"/>
-    </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B189" s="21"/>
-    </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B190" s="21"/>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B191" s="21"/>
-    </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B192" s="21"/>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B193" s="21"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B194" s="21"/>
-    </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B195" s="21"/>
-    </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B196" s="21"/>
-    </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B197" s="21"/>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B198" s="21"/>
-    </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B199" s="21"/>
-    </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B200" s="21"/>
-    </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B201" s="21"/>
-    </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B202" s="21"/>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B203" s="21"/>
-    </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B204" s="21"/>
-    </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B205" s="21"/>
-    </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B206" s="21"/>
-    </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B207" s="21"/>
-    </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B208" s="21"/>
-    </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B209" s="21"/>
-    </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B210" s="21"/>
-    </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B211" s="21"/>
-    </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B212" s="21"/>
-    </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B213" s="21"/>
-    </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B214" s="21"/>
-    </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B215" s="21"/>
-    </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B216" s="21"/>
-    </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B217" s="21"/>
-    </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B218" s="21"/>
+    <row r="151" spans="2:2">
+      <c r="B151" s="20"/>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152" s="20"/>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153" s="20"/>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154" s="20"/>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155" s="20"/>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156" s="20"/>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157" s="20"/>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158" s="20"/>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159" s="20"/>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160" s="20"/>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="20"/>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="20"/>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163" s="20"/>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164" s="20"/>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165" s="20"/>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166" s="20"/>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167" s="20"/>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168" s="20"/>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169" s="20"/>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170" s="20"/>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171" s="20"/>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172" s="20"/>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173" s="20"/>
+    </row>
+    <row r="174" spans="2:2">
+      <c r="B174" s="20"/>
+    </row>
+    <row r="175" spans="2:2">
+      <c r="B175" s="20"/>
+    </row>
+    <row r="176" spans="2:2">
+      <c r="B176" s="20"/>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="20"/>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="20"/>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="20"/>
+    </row>
+    <row r="180" spans="2:2">
+      <c r="B180" s="20"/>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181" s="20"/>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182" s="20"/>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183" s="20"/>
+    </row>
+    <row r="184" spans="2:2">
+      <c r="B184" s="20"/>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185" s="20"/>
+    </row>
+    <row r="186" spans="2:2">
+      <c r="B186" s="20"/>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187" s="20"/>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188" s="20"/>
+    </row>
+    <row r="189" spans="2:2">
+      <c r="B189" s="20"/>
+    </row>
+    <row r="190" spans="2:2">
+      <c r="B190" s="20"/>
+    </row>
+    <row r="191" spans="2:2">
+      <c r="B191" s="20"/>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192" s="20"/>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193" s="20"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="20"/>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="20"/>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="20"/>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="20"/>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198" s="20"/>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199" s="20"/>
+    </row>
+    <row r="200" spans="2:2">
+      <c r="B200" s="20"/>
+    </row>
+    <row r="201" spans="2:2">
+      <c r="B201" s="20"/>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202" s="20"/>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203" s="20"/>
+    </row>
+    <row r="204" spans="2:2">
+      <c r="B204" s="20"/>
+    </row>
+    <row r="205" spans="2:2">
+      <c r="B205" s="20"/>
+    </row>
+    <row r="206" spans="2:2">
+      <c r="B206" s="20"/>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207" s="20"/>
+    </row>
+    <row r="208" spans="2:2">
+      <c r="B208" s="20"/>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209" s="20"/>
+    </row>
+    <row r="210" spans="2:2">
+      <c r="B210" s="20"/>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211" s="20"/>
+    </row>
+    <row r="212" spans="2:2">
+      <c r="B212" s="20"/>
+    </row>
+    <row r="213" spans="2:2">
+      <c r="B213" s="20"/>
+    </row>
+    <row r="214" spans="2:2">
+      <c r="B214" s="20"/>
+    </row>
+    <row r="215" spans="2:2">
+      <c r="B215" s="20"/>
+    </row>
+    <row r="216" spans="2:2">
+      <c r="B216" s="20"/>
+    </row>
+    <row r="217" spans="2:2">
+      <c r="B217" s="20"/>
+    </row>
+    <row r="218" spans="2:2">
+      <c r="B218" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5766,7 +5840,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB14FF3-77DA-4F15-BE17-E8C413F8CD5E}">
   <dimension ref="A3:AJ218"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
@@ -5790,7 +5864,7 @@
     <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>85</v>
       </c>
@@ -5829,7 +5903,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -5859,7 +5933,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -5873,7 +5947,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>169</v>
       </c>
@@ -5887,7 +5961,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>170</v>
       </c>
@@ -5901,7 +5975,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>171</v>
       </c>
@@ -5915,7 +5989,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -5929,7 +6003,7 @@
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>173</v>
       </c>
@@ -5943,7 +6017,7 @@
       <c r="P10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>174</v>
       </c>
@@ -5957,7 +6031,7 @@
       <c r="P11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>175</v>
       </c>
@@ -5971,7 +6045,7 @@
       <c r="P12" s="6"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>176</v>
       </c>
@@ -5985,7 +6059,7 @@
       <c r="P13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>177</v>
       </c>
@@ -5999,7 +6073,7 @@
       <c r="P14" s="6"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>178</v>
       </c>
@@ -6012,7 +6086,7 @@
       <c r="P15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -6021,7 +6095,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>180</v>
       </c>
@@ -6033,7 +6107,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>181</v>
       </c>
@@ -6042,7 +6116,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -6054,7 +6128,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>183</v>
       </c>
@@ -6063,7 +6137,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>184</v>
       </c>
@@ -6075,7 +6149,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>185</v>
       </c>
@@ -6087,7 +6161,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>186</v>
       </c>
@@ -6099,7 +6173,7 @@
       <c r="G23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>187</v>
       </c>
@@ -6108,7 +6182,7 @@
       <c r="G24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>188</v>
       </c>
@@ -6120,7 +6194,7 @@
       <c r="G25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>189</v>
       </c>
@@ -6129,7 +6203,7 @@
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -6141,7 +6215,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>191</v>
       </c>
@@ -6150,7 +6224,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>192</v>
       </c>
@@ -6163,7 +6237,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>193</v>
       </c>
@@ -6176,7 +6250,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>194</v>
       </c>
@@ -6189,7 +6263,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>195</v>
       </c>
@@ -6199,7 +6273,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>196</v>
       </c>
@@ -6211,7 +6285,7 @@
       <c r="G33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -6220,7 +6294,7 @@
       <c r="G34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>198</v>
       </c>
@@ -6233,7 +6307,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>199</v>
       </c>
@@ -6243,7 +6317,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>200</v>
       </c>
@@ -6256,7 +6330,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>201</v>
       </c>
@@ -6269,7 +6343,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>202</v>
       </c>
@@ -6282,7 +6356,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -6292,7 +6366,7 @@
       <c r="H40" s="9"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>204</v>
       </c>
@@ -6305,7 +6379,7 @@
       <c r="H41" s="9"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -6315,7 +6389,7 @@
       <c r="H42" s="9"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>206</v>
       </c>
@@ -6328,7 +6402,7 @@
       <c r="H43" s="9"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>207</v>
       </c>
@@ -6338,215 +6412,215 @@
       <c r="H44" s="9"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:2">
       <c r="B212" s="5"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:2">
       <c r="B213" s="5"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:2">
       <c r="B214" s="5"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:2">
       <c r="B215" s="5"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:2">
       <c r="B216" s="5"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:2">
       <c r="B217" s="5"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:2">
       <c r="B218" s="5"/>
     </row>
   </sheetData>
@@ -6589,7 +6663,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC7F4074-9E65-434B-897B-FD6EE64CA765}">
   <dimension ref="A3:AJ218"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
@@ -6613,7 +6687,7 @@
     <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>237</v>
       </c>
@@ -6652,7 +6726,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -6682,7 +6756,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -6696,7 +6770,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>169</v>
       </c>
@@ -6710,7 +6784,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>170</v>
       </c>
@@ -6724,7 +6798,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>171</v>
       </c>
@@ -6735,7 +6809,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -6749,7 +6823,7 @@
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>173</v>
       </c>
@@ -6760,7 +6834,7 @@
       <c r="P10" s="6"/>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>174</v>
       </c>
@@ -6774,7 +6848,7 @@
       <c r="P11" s="6"/>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>175</v>
       </c>
@@ -6785,7 +6859,7 @@
       <c r="P12" s="6"/>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>176</v>
       </c>
@@ -6799,7 +6873,7 @@
       <c r="P13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>177</v>
       </c>
@@ -6813,7 +6887,7 @@
       <c r="P14" s="6"/>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>178</v>
       </c>
@@ -6826,7 +6900,7 @@
       <c r="P15" s="6"/>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -6835,7 +6909,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>180</v>
       </c>
@@ -6847,7 +6921,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>181</v>
       </c>
@@ -6856,7 +6930,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -6868,7 +6942,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>183</v>
       </c>
@@ -6877,7 +6951,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>184</v>
       </c>
@@ -6889,7 +6963,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>185</v>
       </c>
@@ -6901,7 +6975,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>186</v>
       </c>
@@ -6913,7 +6987,7 @@
       <c r="G23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>187</v>
       </c>
@@ -6922,7 +6996,7 @@
       <c r="G24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>188</v>
       </c>
@@ -6934,7 +7008,7 @@
       <c r="G25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>189</v>
       </c>
@@ -6943,7 +7017,7 @@
       <c r="G26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -6955,7 +7029,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>191</v>
       </c>
@@ -6964,7 +7038,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>192</v>
       </c>
@@ -6977,7 +7051,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>193</v>
       </c>
@@ -6990,7 +7064,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>194</v>
       </c>
@@ -7003,7 +7077,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>195</v>
       </c>
@@ -7013,7 +7087,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>196</v>
       </c>
@@ -7025,7 +7099,7 @@
       <c r="G33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -7034,7 +7108,7 @@
       <c r="G34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>198</v>
       </c>
@@ -7047,7 +7121,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>199</v>
       </c>
@@ -7057,7 +7131,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>200</v>
       </c>
@@ -7070,7 +7144,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>201</v>
       </c>
@@ -7083,7 +7157,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>202</v>
       </c>
@@ -7096,7 +7170,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -7106,7 +7180,7 @@
       <c r="H40" s="9"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>204</v>
       </c>
@@ -7119,7 +7193,7 @@
       <c r="H41" s="9"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -7129,7 +7203,7 @@
       <c r="H42" s="9"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>206</v>
       </c>
@@ -7142,7 +7216,7 @@
       <c r="H43" s="9"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>207</v>
       </c>
@@ -7152,215 +7226,215 @@
       <c r="H44" s="9"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="9"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:2">
       <c r="B212" s="5"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:2">
       <c r="B213" s="5"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:2">
       <c r="B214" s="5"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:2">
       <c r="B215" s="5"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:2">
       <c r="B216" s="5"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:2">
       <c r="B217" s="5"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:2">
       <c r="B218" s="5"/>
     </row>
   </sheetData>
@@ -7403,7 +7477,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1DEF80-1767-4678-9A0F-3D65DA9959F4}">
   <dimension ref="A3:AJ202"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="22.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
@@ -7427,7 +7501,7 @@
     <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>343</v>
       </c>
@@ -7466,7 +7540,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -7496,7 +7570,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>345</v>
       </c>
@@ -7510,7 +7584,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>346</v>
       </c>
@@ -7524,7 +7598,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>351</v>
       </c>
@@ -7537,7 +7611,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>375</v>
       </c>
@@ -7550,7 +7624,7 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>353</v>
       </c>
@@ -7562,7 +7636,7 @@
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>354</v>
       </c>
@@ -7574,7 +7648,7 @@
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>355</v>
       </c>
@@ -7586,7 +7660,7 @@
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>356</v>
       </c>
@@ -7598,7 +7672,7 @@
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>357</v>
       </c>
@@ -7610,7 +7684,7 @@
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>338</v>
       </c>
@@ -7622,7 +7696,7 @@
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>358</v>
       </c>
@@ -7634,7 +7708,7 @@
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
         <v>436</v>
       </c>
@@ -7646,7 +7720,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>359</v>
       </c>
@@ -7658,7 +7732,7 @@
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>377</v>
       </c>
@@ -7670,7 +7744,7 @@
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>379</v>
       </c>
@@ -7682,7 +7756,7 @@
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>381</v>
       </c>
@@ -7694,7 +7768,7 @@
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>383</v>
       </c>
@@ -7706,7 +7780,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>385</v>
       </c>
@@ -7718,7 +7792,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>387</v>
       </c>
@@ -7731,7 +7805,7 @@
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>389</v>
       </c>
@@ -7744,7 +7818,7 @@
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>391</v>
       </c>
@@ -7757,7 +7831,7 @@
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>393</v>
       </c>
@@ -7770,7 +7844,7 @@
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>395</v>
       </c>
@@ -7782,7 +7856,7 @@
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>396</v>
       </c>
@@ -7794,7 +7868,7 @@
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>397</v>
       </c>
@@ -7807,7 +7881,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>398</v>
       </c>
@@ -7820,7 +7894,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>399</v>
       </c>
@@ -7833,7 +7907,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>400</v>
       </c>
@@ -7846,7 +7920,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>401</v>
       </c>
@@ -7859,7 +7933,7 @@
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>412</v>
       </c>
@@ -7872,7 +7946,7 @@
       <c r="H34" s="9"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>415</v>
       </c>
@@ -7885,7 +7959,7 @@
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>419</v>
       </c>
@@ -7898,7 +7972,7 @@
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>420</v>
       </c>
@@ -7911,7 +7985,7 @@
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>421</v>
       </c>
@@ -7924,7 +7998,7 @@
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>422</v>
       </c>
@@ -7937,7 +8011,7 @@
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>430</v>
       </c>
@@ -7945,7 +8019,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>432</v>
       </c>
@@ -7953,7 +8027,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>437</v>
       </c>
@@ -7961,7 +8035,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>508</v>
       </c>
@@ -7969,7 +8043,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>511</v>
       </c>
@@ -7977,7 +8051,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>513</v>
       </c>
@@ -7985,208 +8059,264 @@
         <v>514</v>
       </c>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16">
+      <c r="A46" t="s">
+        <v>516</v>
+      </c>
+      <c r="B46" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" t="s">
+        <v>522</v>
+      </c>
+      <c r="B47" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" t="s">
+        <v>519</v>
+      </c>
+      <c r="B48" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>525</v>
+      </c>
+      <c r="B49" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>526</v>
+      </c>
+      <c r="B50" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>527</v>
+      </c>
+      <c r="B51" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>528</v>
+      </c>
+      <c r="B52" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2">
       <c r="B135" s="5"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:2">
       <c r="B136" s="5"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:2">
       <c r="B137" s="5"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:2">
       <c r="B138" s="5"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:2">
       <c r="B139" s="5"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:2">
       <c r="B140" s="5"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:2">
       <c r="B141" s="5"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:2">
       <c r="B142" s="5"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:2">
       <c r="B143" s="5"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:2">
       <c r="B144" s="5"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:2">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:2">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:2">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:2">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:2">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:2">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
   </sheetData>
@@ -8229,7 +8359,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448EFE5B-7539-4545-AC12-95181FCEF528}">
   <dimension ref="A3:AJ197"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
@@ -8253,7 +8383,7 @@
     <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>344</v>
       </c>
@@ -8292,7 +8422,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -8322,7 +8452,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>345</v>
       </c>
@@ -8334,7 +8464,7 @@
       <c r="G5" s="6"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>346</v>
       </c>
@@ -8346,7 +8476,7 @@
       <c r="G6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="A7" t="s">
         <v>351</v>
       </c>
@@ -8358,7 +8488,7 @@
       <c r="G7" s="6"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="A8" t="s">
         <v>375</v>
       </c>
@@ -8370,7 +8500,7 @@
       <c r="G8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="A9" t="s">
         <v>353</v>
       </c>
@@ -8382,7 +8512,7 @@
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="A10" t="s">
         <v>354</v>
       </c>
@@ -8394,7 +8524,7 @@
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="A11" t="s">
         <v>355</v>
       </c>
@@ -8406,7 +8536,7 @@
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="A12" t="s">
         <v>356</v>
       </c>
@@ -8418,7 +8548,7 @@
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="A13" t="s">
         <v>357</v>
       </c>
@@ -8430,7 +8560,7 @@
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="A14" t="s">
         <v>338</v>
       </c>
@@ -8442,7 +8572,7 @@
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="A15" t="s">
         <v>358</v>
       </c>
@@ -8454,7 +8584,7 @@
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="A16" t="s">
         <v>436</v>
       </c>
@@ -8466,7 +8596,7 @@
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>359</v>
       </c>
@@ -8479,7 +8609,7 @@
       <c r="H17" s="9"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>377</v>
       </c>
@@ -8492,7 +8622,7 @@
       <c r="H18" s="9"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>379</v>
       </c>
@@ -8505,7 +8635,7 @@
       <c r="H19" s="9"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>381</v>
       </c>
@@ -8518,7 +8648,7 @@
       <c r="H20" s="9"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>383</v>
       </c>
@@ -8530,7 +8660,7 @@
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>385</v>
       </c>
@@ -8542,7 +8672,7 @@
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>387</v>
       </c>
@@ -8555,7 +8685,7 @@
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>389</v>
       </c>
@@ -8568,7 +8698,7 @@
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>391</v>
       </c>
@@ -8581,7 +8711,7 @@
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>393</v>
       </c>
@@ -8594,7 +8724,7 @@
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>395</v>
       </c>
@@ -8607,7 +8737,7 @@
       <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>396</v>
       </c>
@@ -8620,7 +8750,7 @@
       <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>397</v>
       </c>
@@ -8633,7 +8763,7 @@
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>398</v>
       </c>
@@ -8646,7 +8776,7 @@
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>399</v>
       </c>
@@ -8659,7 +8789,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>400</v>
       </c>
@@ -8672,7 +8802,7 @@
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>401</v>
       </c>
@@ -8685,7 +8815,7 @@
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>412</v>
       </c>
@@ -8693,7 +8823,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>414</v>
       </c>
@@ -8701,7 +8831,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>419</v>
       </c>
@@ -8709,7 +8839,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>420</v>
       </c>
@@ -8717,7 +8847,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>421</v>
       </c>
@@ -8725,7 +8855,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>422</v>
       </c>
@@ -8733,7 +8863,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>430</v>
       </c>
@@ -8741,7 +8871,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>432</v>
       </c>
@@ -8749,7 +8879,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>437</v>
       </c>
@@ -8757,7 +8887,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>508</v>
       </c>
@@ -8765,7 +8895,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>511</v>
       </c>
@@ -8773,7 +8903,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>513</v>
       </c>
@@ -8781,208 +8911,264 @@
         <v>513</v>
       </c>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16">
+      <c r="A46" t="s">
+        <v>516</v>
+      </c>
+      <c r="B46" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" t="s">
+        <v>522</v>
+      </c>
+      <c r="B47" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" t="s">
+        <v>519</v>
+      </c>
+      <c r="B48" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>525</v>
+      </c>
+      <c r="B49" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>526</v>
+      </c>
+      <c r="B50" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>527</v>
+      </c>
+      <c r="B51" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>528</v>
+      </c>
+      <c r="B52" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
       <c r="B130" s="5"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:2">
       <c r="B131" s="5"/>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:2">
       <c r="B132" s="5"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:2">
       <c r="B133" s="5"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:2">
       <c r="B134" s="5"/>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:2">
       <c r="B135" s="5"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:2">
       <c r="B136" s="5"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:2">
       <c r="B137" s="5"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:2">
       <c r="B138" s="5"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:2">
       <c r="B139" s="5"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:2">
       <c r="B140" s="5"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:2">
       <c r="B141" s="5"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:2">
       <c r="B142" s="5"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:2">
       <c r="B143" s="5"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:2">
       <c r="B144" s="5"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:2">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:2">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:2">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:2">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:2">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:2">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
   </sheetData>
@@ -9025,7 +9211,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D9F6-C7CE-4D6D-A307-34F0A02C664A}">
   <dimension ref="A3:AJ212"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.375" bestFit="1" customWidth="1"/>
@@ -9049,7 +9235,7 @@
     <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>367</v>
       </c>
@@ -9088,7 +9274,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -9118,7 +9304,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>369</v>
       </c>
@@ -9132,7 +9318,7 @@
       <c r="P5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>370</v>
       </c>
@@ -9146,7 +9332,7 @@
       <c r="P6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -9154,7 +9340,7 @@
       <c r="P7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -9162,410 +9348,410 @@
       <c r="P8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:16">
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:16">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:16">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:16">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:16">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:16">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:16">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:16">
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:16">
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:16">
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:16">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:16">
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:16">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:16">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:16">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:16">
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:16">
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:16">
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:16">
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:16">
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="9"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="5:16">
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="5:16">
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="9"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:16">
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="9"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:2">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:2">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:2">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:2">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:2">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:2">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2">
       <c r="B207" s="5"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2">
       <c r="B208" s="5"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2">
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2">
       <c r="B210" s="5"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2">
       <c r="B211" s="5"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:2">
       <c r="B212" s="5"/>
     </row>
   </sheetData>
@@ -9608,7 +9794,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC371501-4D80-4BA3-AE38-ACD1D9A5C0BD}">
   <dimension ref="A3:AJ206"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="85.875" bestFit="1" customWidth="1"/>
@@ -9632,7 +9818,7 @@
     <col min="23" max="32" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>368</v>
       </c>
@@ -9671,7 +9857,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -9701,7 +9887,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36">
       <c r="A5" t="s">
         <v>369</v>
       </c>
@@ -9713,7 +9899,7 @@
       <c r="G5" s="6"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36">
       <c r="A6" t="s">
         <v>370</v>
       </c>
@@ -9725,128 +9911,128 @@
       <c r="G6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36">
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36">
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36">
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36">
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36">
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36">
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36">
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36">
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36">
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36">
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16">
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16">
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16">
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16">
       <c r="B26" s="9"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -9854,257 +10040,257 @@
       <c r="H26" s="9"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16">
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16">
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:16">
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:2">
       <c r="B139" s="5"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:2">
       <c r="B140" s="5"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:2">
       <c r="B141" s="5"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:2">
       <c r="B142" s="5"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:2">
       <c r="B143" s="5"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:2">
       <c r="B144" s="5"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:2">
       <c r="B145" s="5"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:2">
       <c r="B146" s="5"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:2">
       <c r="B147" s="5"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:2">
       <c r="B148" s="5"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:2">
       <c r="B149" s="5"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:2">
       <c r="B150" s="5"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:2">
       <c r="B151" s="5"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:2">
       <c r="B152" s="5"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:2">
       <c r="B153" s="5"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:2">
       <c r="B154" s="5"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:2">
       <c r="B155" s="5"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:2">
       <c r="B156" s="5"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:2">
       <c r="B157" s="5"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:2">
       <c r="B158" s="5"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:2">
       <c r="B159" s="5"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:2">
       <c r="B160" s="5"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2">
       <c r="B161" s="5"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2">
       <c r="B162" s="5"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2">
       <c r="B163" s="5"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2">
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2">
       <c r="B165" s="5"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2">
       <c r="B166" s="5"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2">
       <c r="B167" s="5"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2">
       <c r="B168" s="5"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:2">
       <c r="B169" s="5"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:2">
       <c r="B170" s="5"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:2">
       <c r="B171" s="5"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:2">
       <c r="B172" s="5"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:2">
       <c r="B173" s="5"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:2">
       <c r="B174" s="5"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:2">
       <c r="B175" s="5"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:2">
       <c r="B176" s="5"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:2">
       <c r="B177" s="5"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:2">
       <c r="B178" s="5"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:2">
       <c r="B179" s="5"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:2">
       <c r="B180" s="5"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2">
       <c r="B181" s="5"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2">
       <c r="B182" s="5"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:2">
       <c r="B183" s="5"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:2">
       <c r="B184" s="5"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:2">
       <c r="B185" s="5"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:2">
       <c r="B186" s="5"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:2">
       <c r="B187" s="5"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:2">
       <c r="B188" s="5"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:2">
       <c r="B189" s="5"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:2">
       <c r="B190" s="5"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:2">
       <c r="B191" s="5"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:2">
       <c r="B192" s="5"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2">
       <c r="B193" s="5"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2">
       <c r="B194" s="5"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2">
       <c r="B195" s="5"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2">
       <c r="B196" s="5"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2">
       <c r="B197" s="5"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2">
       <c r="B198" s="5"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2">
       <c r="B199" s="5"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2">
       <c r="B200" s="5"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2">
       <c r="B201" s="5"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2">
       <c r="B202" s="5"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2">
       <c r="B203" s="5"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2">
       <c r="B204" s="5"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2">
       <c r="B205" s="5"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2">
       <c r="B206" s="5"/>
     </row>
   </sheetData>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E616ED17-2B1F-43D5-85D1-9ED4B3F2CC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3F4F83-9019-4379-A925-046E20A767FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="542">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1982,6 +1982,30 @@
   </si>
   <si>
     <t>Ambient Volume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShopItems</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상점 아이템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 아이템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Store Items</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>My Items</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MyItems</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8115,6 +8139,22 @@
         <v>532</v>
       </c>
     </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>536</v>
+      </c>
+      <c r="B53" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>541</v>
+      </c>
+      <c r="B54" t="s">
+        <v>538</v>
+      </c>
+    </row>
     <row r="135" spans="2:2">
       <c r="B135" s="5"/>
     </row>
@@ -8967,6 +9007,22 @@
         <v>535</v>
       </c>
     </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>536</v>
+      </c>
+      <c r="B53" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>541</v>
+      </c>
+      <c r="B54" t="s">
+        <v>540</v>
+      </c>
+    </row>
     <row r="130" spans="2:2">
       <c r="B130" s="5"/>
     </row>

--- a/Sheets/StringData.xlsx
+++ b/Sheets/StringData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3F4F83-9019-4379-A925-046E20A767FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237C7F4F-BC3B-44F2-AAE1-8A2C1DDC5629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects_Ko" sheetId="6" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="562">
   <si>
     <t>$StringId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2006,6 +2006,85 @@
   </si>
   <si>
     <t>MyItems</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Move</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Close Menu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESCDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LeftClickDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RightClickDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도구 사용 또는 아이템 배치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수확/대화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴 닫기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use tool or place item</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check/Do Action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MiddleClickDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Switch Item</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리 핫키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invetory Hotkeys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hotkeys</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8155,6 +8234,62 @@
         <v>538</v>
       </c>
     </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>542</v>
+      </c>
+      <c r="B55" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>544</v>
+      </c>
+      <c r="B56" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>546</v>
+      </c>
+      <c r="B57" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>547</v>
+      </c>
+      <c r="B58" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>548</v>
+      </c>
+      <c r="B59" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>556</v>
+      </c>
+      <c r="B60" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>561</v>
+      </c>
+      <c r="B61" t="s">
+        <v>559</v>
+      </c>
+    </row>
     <row r="135" spans="2:2">
       <c r="B135" s="5"/>
     </row>
@@ -9023,6 +9158,62 @@
         <v>540</v>
       </c>
     </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>542</v>
+      </c>
+      <c r="B55" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>544</v>
+      </c>
+      <c r="B56" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>546</v>
+      </c>
+      <c r="B57" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>547</v>
+      </c>
+      <c r="B58" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>548</v>
+      </c>
+      <c r="B59" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>556</v>
+      </c>
+      <c r="B60" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>561</v>
+      </c>
+      <c r="B61" t="s">
+        <v>560</v>
+      </c>
+    </row>
     <row r="130" spans="2:2">
       <c r="B130" s="5"/>
     </row>
